--- a/develop/day22-excel-file.xlsx
+++ b/develop/day22-excel-file.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
@@ -49,7 +49,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,6 +88,11 @@
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1888,11 +1893,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="6702617"/>
-        <c:axId val="50491802"/>
+        <c:axId val="17228425"/>
+        <c:axId val="29927723"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="6702617"/>
+        <c:axId val="17228425"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1923,12 +1928,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50491802"/>
+        <c:crossAx val="29927723"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="50491802"/>
+        <c:axId val="29927723"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1968,7 +1973,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6702617"/>
+        <c:crossAx val="17228425"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2514,390 +2519,390 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="129"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>-1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.99</c:v>
+                  <c:v>-1.01</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.98000099004983</c:v>
+                  <c:v>-1.01999900995017</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.97000491084453</c:v>
+                  <c:v>-1.02999508915547</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.96001364485433</c:v>
+                  <c:v>-1.03998635514567</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.95002901748536</c:v>
+                  <c:v>-1.04997098251465</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.94005279822097</c:v>
+                  <c:v>-1.05994720177903</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.93008670174418</c:v>
+                  <c:v>-1.06991329825582</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.92013238904135</c:v>
+                  <c:v>-1.07986761095865</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.91019146848752</c:v>
+                  <c:v>-1.08980853151248</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.90026549691353</c:v>
+                  <c:v>-1.09973450308647</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.89035598065533</c:v>
+                  <c:v>-1.10964401934467</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.8804643765857</c:v>
+                  <c:v>-1.1195356234143</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.87059209312859</c:v>
+                  <c:v>-1.12940790687141</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.86074049125642</c:v>
+                  <c:v>-1.13925950874358</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.85091088547055</c:v>
+                  <c:v>-1.14908911452945</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.84110454476525</c:v>
+                  <c:v>-1.15889545523475</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.83132269357523</c:v>
+                  <c:v>-1.16867730642478</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.82156651270722</c:v>
+                  <c:v>-1.17843348729278</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.81183714025572</c:v>
+                  <c:v>-1.18816285974428</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2.80213567250307</c:v>
+                  <c:v>-1.19786432749693</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2.7924631648043</c:v>
+                  <c:v>-1.2075368351957</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.78282063245678</c:v>
+                  <c:v>-1.21717936754322</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.77320905155499</c:v>
+                  <c:v>-1.22679094844501</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2.76362935983071</c:v>
+                  <c:v>-1.23637064016929</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2.75408245747869</c:v>
+                  <c:v>-1.24591754252131</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2.74456920796811</c:v>
+                  <c:v>-1.25543079203189</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2.73509043884011</c:v>
+                  <c:v>-1.26490956115989</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2.72564694249148</c:v>
+                  <c:v>-1.27435305750852</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2.71623947694478</c:v>
+                  <c:v>-1.28376052305522</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2.70686876660512</c:v>
+                  <c:v>-1.29313123339488</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2.69753550300373</c:v>
+                  <c:v>-1.30246449699627</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2.68824034552866</c:v>
+                  <c:v>-1.31175965447134</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2.67898392214263</c:v>
+                  <c:v>-1.32101607785737</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2.66976683008833</c:v>
+                  <c:v>-1.33023316991167</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>2.66058963658145</c:v>
+                  <c:v>-1.33941036341855</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>2.65145287949135</c:v>
+                  <c:v>-1.34854712050865</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2.64235706800994</c:v>
+                  <c:v>-1.35764293199006</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>2.63330268330858</c:v>
+                  <c:v>-1.36669731669142</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2.62429017918349</c:v>
+                  <c:v>-1.37570982081651</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2.6153199826896</c:v>
+                  <c:v>-1.3846800173104</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2.60639249476326</c:v>
+                  <c:v>-1.39360750523675</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2.59750809083373</c:v>
+                  <c:v>-1.40249190916627</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2.58866712142389</c:v>
+                  <c:v>-1.41133287857611</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2.57986991274003</c:v>
+                  <c:v>-1.42013008725997</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2.57111676725125</c:v>
+                  <c:v>-1.42888323274875</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2.56240796425828</c:v>
+                  <c:v>-1.43759203574172</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2.55374376045217</c:v>
+                  <c:v>-1.44625623954783</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2.54512439046281</c:v>
+                  <c:v>-1.45487560953719</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2.53655006739753</c:v>
+                  <c:v>-1.46344993260247</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>2.52802098336997</c:v>
+                  <c:v>-1.47197901663003</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>2.51953731001925</c:v>
+                  <c:v>-1.48046268998075</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2.51109919901974</c:v>
+                  <c:v>-1.48890080098026</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>2.50270678258145</c:v>
+                  <c:v>-1.49729321741855</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>2.49436017394128</c:v>
+                  <c:v>-1.50563982605872</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>2.4860594678452</c:v>
+                  <c:v>-1.5139405321548</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>2.4778047410216</c:v>
+                  <c:v>-1.5221952589784</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>2.46959605264583</c:v>
+                  <c:v>-1.53040394735417</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>2.46143344479617</c:v>
+                  <c:v>-1.53856655520383</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>2.45331694290129</c:v>
+                  <c:v>-1.54668305709871</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>2.44524655617946</c:v>
+                  <c:v>-1.55475344382055</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>2.43722227806939</c:v>
+                  <c:v>-1.56277772193061</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>2.42924408665322</c:v>
+                  <c:v>-1.57075591334678</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>2.42131194507133</c:v>
+                  <c:v>-1.57868805492867</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>2.41342580192953</c:v>
+                  <c:v>-1.58657419807047</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>2.40558559169841</c:v>
+                  <c:v>-1.59441440830159</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>2.39779123510523</c:v>
+                  <c:v>-1.60220876489478</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>2.39004263951827</c:v>
+                  <c:v>-1.60995736048173</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>2.38233969932396</c:v>
+                  <c:v>-1.61766030067605</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>2.37468229629665</c:v>
+                  <c:v>-1.62531770370335</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>2.36707029996148</c:v>
+                  <c:v>-1.63292970003852</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>2.35950356795006</c:v>
+                  <c:v>-1.64049643204995</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>2.35198194634946</c:v>
+                  <c:v>-1.64801805365054</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>2.34450527004435</c:v>
+                  <c:v>-1.65549472995565</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>2.33707336305254</c:v>
+                  <c:v>-1.66292663694746</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>2.32968603885394</c:v>
+                  <c:v>-1.67031396114606</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>2.32234310071311</c:v>
+                  <c:v>-1.6776568992869</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>2.31504434199552</c:v>
+                  <c:v>-1.68495565800449</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>2.30778954647753</c:v>
+                  <c:v>-1.69221045352247</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>2.30057848865031</c:v>
+                  <c:v>-1.69942151134969</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>2.29341093401767</c:v>
+                  <c:v>-1.70658906598233</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>2.28628663938802</c:v>
+                  <c:v>-1.71371336061198</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>2.27920535316051</c:v>
+                  <c:v>-1.72079464683949</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>2.27216681560541</c:v>
+                  <c:v>-1.72783318439459</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>2.26517075913888</c:v>
+                  <c:v>-1.73482924086113</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>2.25821690859219</c:v>
+                  <c:v>-1.74178309140781</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>2.25130498147552</c:v>
+                  <c:v>-1.74869501852448</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>2.24443468823634</c:v>
+                  <c:v>-1.75556531176366</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>2.2376057325126</c:v>
+                  <c:v>-1.7623942674874</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>2.23081781138066</c:v>
+                  <c:v>-1.76918218861934</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>2.22407061559821</c:v>
+                  <c:v>-1.77592938440179</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>2.21736382984211</c:v>
+                  <c:v>-1.78263617015789</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>2.21069713294133</c:v>
+                  <c:v>-1.78930286705867</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>2.20407019810507</c:v>
+                  <c:v>-1.79592980189493</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>2.19748269314608</c:v>
+                  <c:v>-1.80251730685392</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>2.1909342806993</c:v>
+                  <c:v>-1.8090657193007</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>2.18442461843598</c:v>
+                  <c:v>-1.81557538156402</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>2.17795335927313</c:v>
+                  <c:v>-1.82204664072687</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>2.17152015157864</c:v>
+                  <c:v>-1.82847984842136</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>2.16512463937201</c:v>
+                  <c:v>-1.83487536062799</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>2.15876646252072</c:v>
+                  <c:v>-1.84123353747928</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>2.15244525693243</c:v>
+                  <c:v>-1.84755474306757</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>2.14616065474304</c:v>
+                  <c:v>-1.85383934525696</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>2.1399122845006</c:v>
+                  <c:v>-1.8600877154994</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>2.13369977134528</c:v>
+                  <c:v>-1.86630022865472</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>2.12752273718535</c:v>
+                  <c:v>-1.87247726281465</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>2.1213808008693</c:v>
+                  <c:v>-1.8786191991307</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>2.11527357835417</c:v>
+                  <c:v>-1.88472642164584</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>2.10920068287009</c:v>
+                  <c:v>-1.89079931712991</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>2.10316172508122</c:v>
+                  <c:v>-1.89683827491879</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>2.09715631324295</c:v>
+                  <c:v>-1.90284368675706</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>2.09118405335569</c:v>
+                  <c:v>-1.90881594664431</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>2.0852445493151</c:v>
+                  <c:v>-1.9147554506849</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>2.07933740305885</c:v>
+                  <c:v>-1.92066259694115</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>2.07346221471011</c:v>
+                  <c:v>-1.92653778528989</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>2.06761858271763</c:v>
+                  <c:v>-1.93238141728237</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>2.06180610399267</c:v>
+                  <c:v>-1.93819389600733</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>2.05602437404263</c:v>
+                  <c:v>-1.94397562595738</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>2.05027298710161</c:v>
+                  <c:v>-1.94972701289839</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>2.04455153625789</c:v>
+                  <c:v>-1.95544846374211</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>2.03885961357834</c:v>
+                  <c:v>-1.96114038642166</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>2.03319681022988</c:v>
+                  <c:v>-1.96680318977013</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>2.02756271659801</c:v>
+                  <c:v>-1.97243728340199</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>2.02195692240251</c:v>
+                  <c:v>-1.9780430775975</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>2.01637901681024</c:v>
+                  <c:v>-1.98362098318976</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="59008928"/>
-        <c:axId val="86087673"/>
+        <c:axId val="91438552"/>
+        <c:axId val="40506022"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="59008928"/>
+        <c:axId val="91438552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2939,12 +2944,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86087673"/>
+        <c:crossAx val="40506022"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="86087673"/>
+        <c:axId val="40506022"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2986,7 +2991,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59008928"/>
+        <c:crossAx val="91438552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3045,17 +3050,6 @@
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.0703520730410856"/>
-          <c:y val="0.0420280186791194"/>
-          <c:w val="0.844787693077356"/>
-          <c:h val="0.915499221703358"/>
-        </c:manualLayout>
-      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -3064,7 +3058,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet3!$B$1:$B$1</c:f>
+              <c:f>Sheet3!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3097,15 +3091,11 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -4609,17 +4599,1563 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="63803241"/>
-        <c:axId val="27617122"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>f(x)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet3!$A$2:$A$246</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="245"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.07</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.29</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.31</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.38</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.39</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.43</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.44</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.46</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.47</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.48</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.49</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.51</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.52</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.54</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.55</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.56</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.57</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.58</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.59</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.61</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.62</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>1.01</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>1.02</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>1.03</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>1.04</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>1.05</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>1.06</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>1.07</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>1.08</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>1.09</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>1.1</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>1.11</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>1.12</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>1.13</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>1.14</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>1.15</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>1.16</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>1.17</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>1.18</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>1.19</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>1.21</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>1.22</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>1.23</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>1.24</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>1.26</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>1.27</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>1.28</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>1.29</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>1.31</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>1.32</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>1.33</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>1.34</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>1.35</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>1.36</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>1.37</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>1.38</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>1.39</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>1.41</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>1.42</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>1.43</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>1.44</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>1.45</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>1.46</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>1.47</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>1.48</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>1.49</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>1.51</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>1.52</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>1.53</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>1.54</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>1.55</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>1.56</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>1.57</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>1.58</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>1.59</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>1.61</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>1.62</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>1.63</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>1.64</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>1.65</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>1.66</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>1.67</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>1.68</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>1.69</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>1.71</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>1.72</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>1.73</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>1.74</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>1.75</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>1.76</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>1.77</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>1.78</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>1.79</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>1.81</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>1.82</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>1.83</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>1.84</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>1.85</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>1.86</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>1.87</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>1.88</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>1.89</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>1.91</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>1.92</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>1.93</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>1.94</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>1.95</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>1.96</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>1.97</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>1.98</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>1.99</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>2.01</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>2.02</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>2.03</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>2.04</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>2.05</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>2.06</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>2.07</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>2.08</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>2.09</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>2.1</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>2.11</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>2.12</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>2.13</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>2.14</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>2.15</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>2.16</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>2.17</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>2.18</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>2.19</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>2.2</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>2.21</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>2.22</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>2.23</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>2.24</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>2.25</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>2.26</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>2.27</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>2.28</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>2.29</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>2.3</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>2.31</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>2.32</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>2.34</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>2.35</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>2.36</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>2.37</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>2.38</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>2.39</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>2.41</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>2.42</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>2.43</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>2.44</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet3!$D$2:$D$246</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="245"/>
+                <c:pt idx="0">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.990049833749168</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.980198673306755</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.970445533548508</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.960789439152323</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.951229424500714</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.941764533584249</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.932393819905948</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.923116346386636</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.913931185271228</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.90483741803596</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.895834135296528</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.886920436717158</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.878095430920561</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.869358235398806</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.860707976425058</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.852143788966211</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.843664816596384</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.835270211411272</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.826959133943362</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-0.818730753077982</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-0.810584245970187</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.802518797962479</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-0.794533602503334</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.786627861066554</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-0.778800783071405</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-0.771051585803566</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-0.763379494336853</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-0.755783741455726</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-0.748263567578565</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-0.740818220681718</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-0.733446956224289</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-0.726149037073691</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-0.718923733431926</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-0.71177032276261</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-0.704688089718713</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-0.697676326071031</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-0.690734330637355</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-0.683861409212356</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-0.677056874498165</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-0.670320046035639</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-0.663650250136319</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-0.657046819815057</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-0.650509094723317</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-0.644036421083141</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-0.637628151621773</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-0.631283645506926</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-0.625002268282701</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-0.618783391806141</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-0.612626394184416</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-0.606530659712633</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-0.600495578812266</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-0.594520547970194</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-0.588604969678355</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-0.58274825237399</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-0.576949810380487</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-0.571209063848815</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-0.565525438699537</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-0.559898366565402</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-0.554327284734507</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-0.548811636094026</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-0.5433508690745</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-0.537944437594675</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-0.532591801006897</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-0.527292424043049</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-0.522045776761016</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-0.516851334491699</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-0.511708577786542</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-0.50661699236559</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-0.501576069066056</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-0.49658530379141</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>-0.491644197460965</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>-0.486752255959972</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>-0.481908990090202</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-0.477113915521034</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>-0.472366552741015</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>-0.467666427009909</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>-0.463013068311228</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>-0.458406011305224</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>-0.453844795282356</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>-0.449328964117222</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>-0.444858066222941</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>-0.440431654505999</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>-0.436049286321536</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>-0.43171052342908</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>-0.427414931948727</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>-0.423162082317749</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>-0.418951549247639</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>-0.414782911681581</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>-0.410655752752346</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>-0.406569659740599</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>-0.402524224033636</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>-0.398519041084514</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>-0.394553710371601</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>-0.390627835358521</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>-0.386741023454501</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>-0.382892885975112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>-0.379083038103399</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>-0.3753110988514</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>-0.371576691022046</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>-0.367879441171442</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>-0.364218979571523</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>-0.360594940173078</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>-0.357006960569147</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>-0.35345468195878</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>-0.349937749111155</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>-0.346455810330057</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>-0.343008517418707</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>-0.339595525644939</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>-0.336216493706733</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>-0.33287108369808</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>-0.329558961075189</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>-0.326279794623039</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>-0.323033256422253</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>-0.319819021816304</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>-0.316636769379053</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>-0.313486180882605</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>-0.310366941265485</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>-0.307278738601131</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>-0.304221264066704</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>-0.301194211912202</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>-0.298197279429887</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>-0.295230166924014</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>-0.292292577680859</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>-0.289384217939051</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>-0.28650479686019</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>-0.28365402649977</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>-0.28083162177838</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>-0.278037300453194</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>-0.275270783089752</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>-0.272531793034013</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>-0.269820056384687</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>-0.26713530196585</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>-0.264477261299824</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>-0.261845668580326</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>-0.259240260645892</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>-0.256660776953556</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>-0.2541069595528</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>-0.251578553059757</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>-0.249075304631668</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>-0.246596963941607</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>-0.244143283153437</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>-0.241714016897036</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>-0.239308922243755</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>-0.236927758682122</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>-0.234570288093798</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>-0.232236274729759</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>-0.229925485186724</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>-0.227637688383813</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>-0.225372655539439</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>-0.22313016014843</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>-0.220909977959378</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>-0.218711886952215</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>-0.216535667316007</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>-0.214381101426978</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>-0.212247973826743</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>-0.210136071200765</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>-0.20804518235702</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>-0.205975098204883</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>-0.203925611734213</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>-0.201896517994655</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>-0.199887614075145</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>-0.197898699083615</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>-0.195929574126909</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>-0.193980042290892</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>-0.192049908620754</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>-0.190138980101521</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>-0.188247065638747</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>-0.18637397603941</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>-0.184519523992989</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>-0.182683524052735</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>-0.180865792617122</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>-0.179066147911493</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>-0.177284409969878</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>-0.175520400616997</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>-0.173773943450445</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>-0.172044863823051</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>-0.170332988825409</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>-0.168638147268596</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>-0.166960169667041</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>-0.165298888221587</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>-0.163654136802704</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>-0.162025750933881</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>-0.160413567775173</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>-0.158817426106921</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>-0.157237166313628</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>-0.155672630367997</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>-0.154123661815131</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>-0.152590105756884</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>-0.151071808836371</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>-0.149568619222635</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>-0.148080386595462</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>-0.14660696213035</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>-0.145148198483624</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>-0.143703949777703</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>-0.142274071586514</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>-0.140858420921045</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>-0.139456856215051</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>-0.138069237310893</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>-0.136695425445524</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>-0.135335283236613</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>-0.133988674668805</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>-0.132655465080122</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>-0.131335521148493</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>-0.130028710878426</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>-0.128734903587804</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>-0.127453969894821</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>-0.126185781705039</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>-0.124930212198582</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>-0.123687135817455</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>-0.122456428252982</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>-0.121237966433382</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>-0.120031628511457</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>-0.11883729385241</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>-0.117654843021779</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>-0.116484157773497</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>-0.115325121038063</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>-0.114177616910837</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>-0.11304153064045</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>-0.111916748617329</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>-0.110803158362334</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>-0.109700648515511</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>-0.108609108824958</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>-0.107528430135795</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>-0.106458504379253</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>-0.105399224561864</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>-0.104350484754765</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>-0.1033121800831</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>-0.102284206715537</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>-0.101266461853883</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>-0.100258843722804</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>-0.0992612515596457</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>-0.0982735856043615</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>-0.0972957470895328</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>-0.096327638230493</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>-0.0953691622155496</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>-0.0944202231963024</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>-0.0934807262780585</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>-0.0925505775103433</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>-0.0916296838775048</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>-0.0907179532894125</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>-0.0898152945722476</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>-0.0889216174593863</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>-0.0880368325823726</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>-0.0871608514619813</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:axId val="61199096"/>
+        <c:axId val="22753671"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="63803241"/>
+        <c:axId val="61199096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4636,20 +6172,17 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27617122"/>
+        <c:crossAx val="22753671"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="27617122"/>
+        <c:axId val="22753671"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4664,7 +6197,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4681,17 +6214,14 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63803241"/>
+        <c:crossAx val="61199096"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -4717,9 +6247,6 @@
         <a:p>
           <a:pPr>
             <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
               <a:latin typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -4745,15 +6272,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>379080</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>75240</xdr:rowOff>
+      <xdr:colOff>1022040</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>176400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>982800</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>154800</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>335160</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>255600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4761,8 +6288,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7265520" y="1129320"/>
-        <a:ext cx="5765040" cy="3241800"/>
+        <a:off x="7908480" y="703440"/>
+        <a:ext cx="5764680" cy="3241440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4779,16 +6306,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>380880</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>162000</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>95400</xdr:rowOff>
+      <xdr:rowOff>17640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>74880</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>543600</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>170640</xdr:rowOff>
+      <xdr:rowOff>92520</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4796,8 +6323,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3819240" y="476280"/>
-        <a:ext cx="5195880" cy="2742480"/>
+        <a:off x="2912760" y="398520"/>
+        <a:ext cx="5195520" cy="2742120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4814,16 +6341,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>235800</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>378000</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>152640</xdr:rowOff>
+      <xdr:rowOff>183240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>490680</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>634680</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>151560</xdr:rowOff>
+      <xdr:rowOff>183240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4831,8 +6358,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5049720" y="533520"/>
-        <a:ext cx="5756400" cy="3237480"/>
+        <a:off x="3816360" y="564120"/>
+        <a:ext cx="5758560" cy="3238560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7707,7 +9234,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="C2" s="2" t="n">
         <f aca="false">A2^2*EXP(-A2)-1</f>
@@ -7720,7 +9247,7 @@
       </c>
       <c r="B3" s="2" t="n">
         <f aca="false">B2+C2*(A3-A2)</f>
-        <v>2.99</v>
+        <v>-1.01</v>
       </c>
       <c r="C3" s="2" t="n">
         <f aca="false">A3^2*EXP(-A3)-1</f>
@@ -7733,7 +9260,7 @@
       </c>
       <c r="B4" s="2" t="n">
         <f aca="false">B3+C3*(A4-A3)</f>
-        <v>2.98000099004983</v>
+        <v>-1.01999900995017</v>
       </c>
       <c r="C4" s="2" t="n">
         <f aca="false">A4^2*EXP(-A4)-1</f>
@@ -7746,7 +9273,7 @@
       </c>
       <c r="B5" s="2" t="n">
         <f aca="false">B4+C4*(A5-A4)</f>
-        <v>2.97000491084453</v>
+        <v>-1.02999508915547</v>
       </c>
       <c r="C5" s="2" t="n">
         <f aca="false">A5^2*EXP(-A5)-1</f>
@@ -7759,7 +9286,7 @@
       </c>
       <c r="B6" s="2" t="n">
         <f aca="false">B5+C5*(A6-A5)</f>
-        <v>2.96001364485433</v>
+        <v>-1.03998635514567</v>
       </c>
       <c r="C6" s="2" t="n">
         <f aca="false">A6^2*EXP(-A6)-1</f>
@@ -7772,7 +9299,7 @@
       </c>
       <c r="B7" s="2" t="n">
         <f aca="false">B6+C6*(A7-A6)</f>
-        <v>2.95002901748536</v>
+        <v>-1.04997098251465</v>
       </c>
       <c r="C7" s="2" t="n">
         <f aca="false">A7^2*EXP(-A7)-1</f>
@@ -7785,7 +9312,7 @@
       </c>
       <c r="B8" s="2" t="n">
         <f aca="false">B7+C7*(A8-A7)</f>
-        <v>2.94005279822097</v>
+        <v>-1.05994720177903</v>
       </c>
       <c r="C8" s="2" t="n">
         <f aca="false">A8^2*EXP(-A8)-1</f>
@@ -7798,7 +9325,7 @@
       </c>
       <c r="B9" s="2" t="n">
         <f aca="false">B8+C8*(A9-A8)</f>
-        <v>2.93008670174418</v>
+        <v>-1.06991329825582</v>
       </c>
       <c r="C9" s="2" t="n">
         <f aca="false">A9^2*EXP(-A9)-1</f>
@@ -7811,7 +9338,7 @@
       </c>
       <c r="B10" s="2" t="n">
         <f aca="false">B9+C9*(A10-A9)</f>
-        <v>2.92013238904135</v>
+        <v>-1.07986761095865</v>
       </c>
       <c r="C10" s="2" t="n">
         <f aca="false">A10^2*EXP(-A10)-1</f>
@@ -7824,7 +9351,7 @@
       </c>
       <c r="B11" s="2" t="n">
         <f aca="false">B10+C10*(A11-A10)</f>
-        <v>2.91019146848752</v>
+        <v>-1.08980853151248</v>
       </c>
       <c r="C11" s="2" t="n">
         <f aca="false">A11^2*EXP(-A11)-1</f>
@@ -7837,7 +9364,7 @@
       </c>
       <c r="B12" s="2" t="n">
         <f aca="false">B11+C11*(A12-A11)</f>
-        <v>2.90026549691353</v>
+        <v>-1.09973450308647</v>
       </c>
       <c r="C12" s="2" t="n">
         <f aca="false">A12^2*EXP(-A12)-1</f>
@@ -7850,7 +9377,7 @@
       </c>
       <c r="B13" s="2" t="n">
         <f aca="false">B12+C12*(A13-A12)</f>
-        <v>2.89035598065533</v>
+        <v>-1.10964401934467</v>
       </c>
       <c r="C13" s="2" t="n">
         <f aca="false">A13^2*EXP(-A13)-1</f>
@@ -7863,7 +9390,7 @@
       </c>
       <c r="B14" s="2" t="n">
         <f aca="false">B13+C13*(A14-A13)</f>
-        <v>2.8804643765857</v>
+        <v>-1.1195356234143</v>
       </c>
       <c r="C14" s="2" t="n">
         <f aca="false">A14^2*EXP(-A14)-1</f>
@@ -7876,7 +9403,7 @@
       </c>
       <c r="B15" s="2" t="n">
         <f aca="false">B14+C14*(A15-A14)</f>
-        <v>2.87059209312859</v>
+        <v>-1.12940790687141</v>
       </c>
       <c r="C15" s="2" t="n">
         <f aca="false">A15^2*EXP(-A15)-1</f>
@@ -7889,7 +9416,7 @@
       </c>
       <c r="B16" s="2" t="n">
         <f aca="false">B15+C15*(A16-A15)</f>
-        <v>2.86074049125642</v>
+        <v>-1.13925950874358</v>
       </c>
       <c r="C16" s="2" t="n">
         <f aca="false">A16^2*EXP(-A16)-1</f>
@@ -7902,7 +9429,7 @@
       </c>
       <c r="B17" s="2" t="n">
         <f aca="false">B16+C16*(A17-A16)</f>
-        <v>2.85091088547055</v>
+        <v>-1.14908911452945</v>
       </c>
       <c r="C17" s="2" t="n">
         <f aca="false">A17^2*EXP(-A17)-1</f>
@@ -7915,7 +9442,7 @@
       </c>
       <c r="B18" s="2" t="n">
         <f aca="false">B17+C17*(A18-A17)</f>
-        <v>2.84110454476525</v>
+        <v>-1.15889545523475</v>
       </c>
       <c r="C18" s="2" t="n">
         <f aca="false">A18^2*EXP(-A18)-1</f>
@@ -7928,7 +9455,7 @@
       </c>
       <c r="B19" s="2" t="n">
         <f aca="false">B18+C18*(A19-A18)</f>
-        <v>2.83132269357523</v>
+        <v>-1.16867730642478</v>
       </c>
       <c r="C19" s="2" t="n">
         <f aca="false">A19^2*EXP(-A19)-1</f>
@@ -7941,7 +9468,7 @@
       </c>
       <c r="B20" s="2" t="n">
         <f aca="false">B19+C19*(A20-A19)</f>
-        <v>2.82156651270722</v>
+        <v>-1.17843348729278</v>
       </c>
       <c r="C20" s="2" t="n">
         <f aca="false">A20^2*EXP(-A20)-1</f>
@@ -7954,7 +9481,7 @@
       </c>
       <c r="B21" s="2" t="n">
         <f aca="false">B20+C20*(A21-A20)</f>
-        <v>2.81183714025572</v>
+        <v>-1.18816285974428</v>
       </c>
       <c r="C21" s="2" t="n">
         <f aca="false">A21^2*EXP(-A21)-1</f>
@@ -7967,7 +9494,7 @@
       </c>
       <c r="B22" s="2" t="n">
         <f aca="false">B21+C21*(A22-A21)</f>
-        <v>2.80213567250307</v>
+        <v>-1.19786432749693</v>
       </c>
       <c r="C22" s="2" t="n">
         <f aca="false">A22^2*EXP(-A22)-1</f>
@@ -7980,7 +9507,7 @@
       </c>
       <c r="B23" s="2" t="n">
         <f aca="false">B22+C22*(A23-A22)</f>
-        <v>2.7924631648043</v>
+        <v>-1.2075368351957</v>
       </c>
       <c r="C23" s="2" t="n">
         <f aca="false">A23^2*EXP(-A23)-1</f>
@@ -7993,7 +9520,7 @@
       </c>
       <c r="B24" s="2" t="n">
         <f aca="false">B23+C23*(A24-A23)</f>
-        <v>2.78282063245678</v>
+        <v>-1.21717936754322</v>
       </c>
       <c r="C24" s="2" t="n">
         <f aca="false">A24^2*EXP(-A24)-1</f>
@@ -8006,7 +9533,7 @@
       </c>
       <c r="B25" s="2" t="n">
         <f aca="false">B24+C24*(A25-A24)</f>
-        <v>2.77320905155499</v>
+        <v>-1.22679094844501</v>
       </c>
       <c r="C25" s="2" t="n">
         <f aca="false">A25^2*EXP(-A25)-1</f>
@@ -8019,7 +9546,7 @@
       </c>
       <c r="B26" s="2" t="n">
         <f aca="false">B25+C25*(A26-A25)</f>
-        <v>2.76362935983071</v>
+        <v>-1.23637064016929</v>
       </c>
       <c r="C26" s="2" t="n">
         <f aca="false">A26^2*EXP(-A26)-1</f>
@@ -8032,7 +9559,7 @@
       </c>
       <c r="B27" s="2" t="n">
         <f aca="false">B26+C26*(A27-A26)</f>
-        <v>2.75408245747869</v>
+        <v>-1.24591754252131</v>
       </c>
       <c r="C27" s="2" t="n">
         <f aca="false">A27^2*EXP(-A27)-1</f>
@@ -8045,7 +9572,7 @@
       </c>
       <c r="B28" s="2" t="n">
         <f aca="false">B27+C27*(A28-A27)</f>
-        <v>2.74456920796811</v>
+        <v>-1.25543079203189</v>
       </c>
       <c r="C28" s="2" t="n">
         <f aca="false">A28^2*EXP(-A28)-1</f>
@@ -8058,7 +9585,7 @@
       </c>
       <c r="B29" s="2" t="n">
         <f aca="false">B28+C28*(A29-A28)</f>
-        <v>2.73509043884011</v>
+        <v>-1.26490956115989</v>
       </c>
       <c r="C29" s="2" t="n">
         <f aca="false">A29^2*EXP(-A29)-1</f>
@@ -8071,7 +9598,7 @@
       </c>
       <c r="B30" s="2" t="n">
         <f aca="false">B29+C29*(A30-A29)</f>
-        <v>2.72564694249148</v>
+        <v>-1.27435305750852</v>
       </c>
       <c r="C30" s="2" t="n">
         <f aca="false">A30^2*EXP(-A30)-1</f>
@@ -8084,7 +9611,7 @@
       </c>
       <c r="B31" s="2" t="n">
         <f aca="false">B30+C30*(A31-A30)</f>
-        <v>2.71623947694478</v>
+        <v>-1.28376052305522</v>
       </c>
       <c r="C31" s="2" t="n">
         <f aca="false">A31^2*EXP(-A31)-1</f>
@@ -8097,7 +9624,7 @@
       </c>
       <c r="B32" s="2" t="n">
         <f aca="false">B31+C31*(A32-A31)</f>
-        <v>2.70686876660512</v>
+        <v>-1.29313123339488</v>
       </c>
       <c r="C32" s="2" t="n">
         <f aca="false">A32^2*EXP(-A32)-1</f>
@@ -8110,7 +9637,7 @@
       </c>
       <c r="B33" s="2" t="n">
         <f aca="false">B32+C32*(A33-A32)</f>
-        <v>2.69753550300373</v>
+        <v>-1.30246449699627</v>
       </c>
       <c r="C33" s="2" t="n">
         <f aca="false">A33^2*EXP(-A33)-1</f>
@@ -8123,7 +9650,7 @@
       </c>
       <c r="B34" s="2" t="n">
         <f aca="false">B33+C33*(A34-A33)</f>
-        <v>2.68824034552866</v>
+        <v>-1.31175965447134</v>
       </c>
       <c r="C34" s="2" t="n">
         <f aca="false">A34^2*EXP(-A34)-1</f>
@@ -8136,7 +9663,7 @@
       </c>
       <c r="B35" s="2" t="n">
         <f aca="false">B34+C34*(A35-A34)</f>
-        <v>2.67898392214263</v>
+        <v>-1.32101607785737</v>
       </c>
       <c r="C35" s="2" t="n">
         <f aca="false">A35^2*EXP(-A35)-1</f>
@@ -8149,7 +9676,7 @@
       </c>
       <c r="B36" s="2" t="n">
         <f aca="false">B35+C35*(A36-A35)</f>
-        <v>2.66976683008833</v>
+        <v>-1.33023316991167</v>
       </c>
       <c r="C36" s="2" t="n">
         <f aca="false">A36^2*EXP(-A36)-1</f>
@@ -8162,7 +9689,7 @@
       </c>
       <c r="B37" s="2" t="n">
         <f aca="false">B36+C36*(A37-A36)</f>
-        <v>2.66058963658145</v>
+        <v>-1.33941036341855</v>
       </c>
       <c r="C37" s="2" t="n">
         <f aca="false">A37^2*EXP(-A37)-1</f>
@@ -8175,7 +9702,7 @@
       </c>
       <c r="B38" s="2" t="n">
         <f aca="false">B37+C37*(A38-A37)</f>
-        <v>2.65145287949135</v>
+        <v>-1.34854712050865</v>
       </c>
       <c r="C38" s="2" t="n">
         <f aca="false">A38^2*EXP(-A38)-1</f>
@@ -8188,7 +9715,7 @@
       </c>
       <c r="B39" s="2" t="n">
         <f aca="false">B38+C38*(A39-A38)</f>
-        <v>2.64235706800994</v>
+        <v>-1.35764293199006</v>
       </c>
       <c r="C39" s="2" t="n">
         <f aca="false">A39^2*EXP(-A39)-1</f>
@@ -8201,7 +9728,7 @@
       </c>
       <c r="B40" s="2" t="n">
         <f aca="false">B39+C39*(A40-A39)</f>
-        <v>2.63330268330858</v>
+        <v>-1.36669731669142</v>
       </c>
       <c r="C40" s="2" t="n">
         <f aca="false">A40^2*EXP(-A40)-1</f>
@@ -8214,7 +9741,7 @@
       </c>
       <c r="B41" s="2" t="n">
         <f aca="false">B40+C40*(A41-A40)</f>
-        <v>2.62429017918349</v>
+        <v>-1.37570982081651</v>
       </c>
       <c r="C41" s="2" t="n">
         <f aca="false">A41^2*EXP(-A41)-1</f>
@@ -8227,7 +9754,7 @@
       </c>
       <c r="B42" s="2" t="n">
         <f aca="false">B41+C41*(A42-A41)</f>
-        <v>2.6153199826896</v>
+        <v>-1.3846800173104</v>
       </c>
       <c r="C42" s="2" t="n">
         <f aca="false">A42^2*EXP(-A42)-1</f>
@@ -8240,7 +9767,7 @@
       </c>
       <c r="B43" s="2" t="n">
         <f aca="false">B42+C42*(A43-A42)</f>
-        <v>2.60639249476326</v>
+        <v>-1.39360750523675</v>
       </c>
       <c r="C43" s="2" t="n">
         <f aca="false">A43^2*EXP(-A43)-1</f>
@@ -8253,7 +9780,7 @@
       </c>
       <c r="B44" s="2" t="n">
         <f aca="false">B43+C43*(A44-A43)</f>
-        <v>2.59750809083373</v>
+        <v>-1.40249190916627</v>
       </c>
       <c r="C44" s="2" t="n">
         <f aca="false">A44^2*EXP(-A44)-1</f>
@@ -8266,7 +9793,7 @@
       </c>
       <c r="B45" s="2" t="n">
         <f aca="false">B44+C44*(A45-A44)</f>
-        <v>2.58866712142389</v>
+        <v>-1.41133287857611</v>
       </c>
       <c r="C45" s="2" t="n">
         <f aca="false">A45^2*EXP(-A45)-1</f>
@@ -8279,7 +9806,7 @@
       </c>
       <c r="B46" s="2" t="n">
         <f aca="false">B45+C45*(A46-A45)</f>
-        <v>2.57986991274003</v>
+        <v>-1.42013008725997</v>
       </c>
       <c r="C46" s="2" t="n">
         <f aca="false">A46^2*EXP(-A46)-1</f>
@@ -8292,7 +9819,7 @@
       </c>
       <c r="B47" s="2" t="n">
         <f aca="false">B46+C46*(A47-A46)</f>
-        <v>2.57111676725125</v>
+        <v>-1.42888323274875</v>
       </c>
       <c r="C47" s="2" t="n">
         <f aca="false">A47^2*EXP(-A47)-1</f>
@@ -8305,7 +9832,7 @@
       </c>
       <c r="B48" s="2" t="n">
         <f aca="false">B47+C47*(A48-A47)</f>
-        <v>2.56240796425828</v>
+        <v>-1.43759203574172</v>
       </c>
       <c r="C48" s="2" t="n">
         <f aca="false">A48^2*EXP(-A48)-1</f>
@@ -8318,7 +9845,7 @@
       </c>
       <c r="B49" s="2" t="n">
         <f aca="false">B48+C48*(A49-A48)</f>
-        <v>2.55374376045217</v>
+        <v>-1.44625623954783</v>
       </c>
       <c r="C49" s="2" t="n">
         <f aca="false">A49^2*EXP(-A49)-1</f>
@@ -8331,7 +9858,7 @@
       </c>
       <c r="B50" s="2" t="n">
         <f aca="false">B49+C49*(A50-A49)</f>
-        <v>2.54512439046281</v>
+        <v>-1.45487560953719</v>
       </c>
       <c r="C50" s="2" t="n">
         <f aca="false">A50^2*EXP(-A50)-1</f>
@@ -8344,7 +9871,7 @@
       </c>
       <c r="B51" s="2" t="n">
         <f aca="false">B50+C50*(A51-A50)</f>
-        <v>2.53655006739753</v>
+        <v>-1.46344993260247</v>
       </c>
       <c r="C51" s="2" t="n">
         <f aca="false">A51^2*EXP(-A51)-1</f>
@@ -8357,7 +9884,7 @@
       </c>
       <c r="B52" s="2" t="n">
         <f aca="false">B51+C51*(A52-A51)</f>
-        <v>2.52802098336997</v>
+        <v>-1.47197901663003</v>
       </c>
       <c r="C52" s="2" t="n">
         <f aca="false">A52^2*EXP(-A52)-1</f>
@@ -8370,7 +9897,7 @@
       </c>
       <c r="B53" s="2" t="n">
         <f aca="false">B52+C52*(A53-A52)</f>
-        <v>2.51953731001925</v>
+        <v>-1.48046268998075</v>
       </c>
       <c r="C53" s="2" t="n">
         <f aca="false">A53^2*EXP(-A53)-1</f>
@@ -8383,7 +9910,7 @@
       </c>
       <c r="B54" s="2" t="n">
         <f aca="false">B53+C53*(A54-A53)</f>
-        <v>2.51109919901974</v>
+        <v>-1.48890080098026</v>
       </c>
       <c r="C54" s="2" t="n">
         <f aca="false">A54^2*EXP(-A54)-1</f>
@@ -8396,7 +9923,7 @@
       </c>
       <c r="B55" s="2" t="n">
         <f aca="false">B54+C54*(A55-A54)</f>
-        <v>2.50270678258145</v>
+        <v>-1.49729321741855</v>
       </c>
       <c r="C55" s="2" t="n">
         <f aca="false">A55^2*EXP(-A55)-1</f>
@@ -8409,7 +9936,7 @@
       </c>
       <c r="B56" s="2" t="n">
         <f aca="false">B55+C55*(A56-A55)</f>
-        <v>2.49436017394128</v>
+        <v>-1.50563982605872</v>
       </c>
       <c r="C56" s="2" t="n">
         <f aca="false">A56^2*EXP(-A56)-1</f>
@@ -8422,7 +9949,7 @@
       </c>
       <c r="B57" s="2" t="n">
         <f aca="false">B56+C56*(A57-A56)</f>
-        <v>2.4860594678452</v>
+        <v>-1.5139405321548</v>
       </c>
       <c r="C57" s="2" t="n">
         <f aca="false">A57^2*EXP(-A57)-1</f>
@@ -8435,7 +9962,7 @@
       </c>
       <c r="B58" s="2" t="n">
         <f aca="false">B57+C57*(A58-A57)</f>
-        <v>2.4778047410216</v>
+        <v>-1.5221952589784</v>
       </c>
       <c r="C58" s="2" t="n">
         <f aca="false">A58^2*EXP(-A58)-1</f>
@@ -8448,7 +9975,7 @@
       </c>
       <c r="B59" s="2" t="n">
         <f aca="false">B58+C58*(A59-A58)</f>
-        <v>2.46959605264583</v>
+        <v>-1.53040394735417</v>
       </c>
       <c r="C59" s="2" t="n">
         <f aca="false">A59^2*EXP(-A59)-1</f>
@@ -8461,7 +9988,7 @@
       </c>
       <c r="B60" s="2" t="n">
         <f aca="false">B59+C59*(A60-A59)</f>
-        <v>2.46143344479617</v>
+        <v>-1.53856655520383</v>
       </c>
       <c r="C60" s="2" t="n">
         <f aca="false">A60^2*EXP(-A60)-1</f>
@@ -8474,7 +10001,7 @@
       </c>
       <c r="B61" s="2" t="n">
         <f aca="false">B60+C60*(A61-A60)</f>
-        <v>2.45331694290129</v>
+        <v>-1.54668305709871</v>
       </c>
       <c r="C61" s="2" t="n">
         <f aca="false">A61^2*EXP(-A61)-1</f>
@@ -8487,7 +10014,7 @@
       </c>
       <c r="B62" s="2" t="n">
         <f aca="false">B61+C61*(A62-A61)</f>
-        <v>2.44524655617946</v>
+        <v>-1.55475344382055</v>
       </c>
       <c r="C62" s="2" t="n">
         <f aca="false">A62^2*EXP(-A62)-1</f>
@@ -8500,7 +10027,7 @@
       </c>
       <c r="B63" s="2" t="n">
         <f aca="false">B62+C62*(A63-A62)</f>
-        <v>2.43722227806939</v>
+        <v>-1.56277772193061</v>
       </c>
       <c r="C63" s="2" t="n">
         <f aca="false">A63^2*EXP(-A63)-1</f>
@@ -8513,7 +10040,7 @@
       </c>
       <c r="B64" s="2" t="n">
         <f aca="false">B63+C63*(A64-A63)</f>
-        <v>2.42924408665322</v>
+        <v>-1.57075591334678</v>
       </c>
       <c r="C64" s="2" t="n">
         <f aca="false">A64^2*EXP(-A64)-1</f>
@@ -8526,7 +10053,7 @@
       </c>
       <c r="B65" s="2" t="n">
         <f aca="false">B64+C64*(A65-A64)</f>
-        <v>2.42131194507133</v>
+        <v>-1.57868805492867</v>
       </c>
       <c r="C65" s="2" t="n">
         <f aca="false">A65^2*EXP(-A65)-1</f>
@@ -8539,7 +10066,7 @@
       </c>
       <c r="B66" s="2" t="n">
         <f aca="false">B65+C65*(A66-A65)</f>
-        <v>2.41342580192953</v>
+        <v>-1.58657419807047</v>
       </c>
       <c r="C66" s="2" t="n">
         <f aca="false">A66^2*EXP(-A66)-1</f>
@@ -8552,7 +10079,7 @@
       </c>
       <c r="B67" s="2" t="n">
         <f aca="false">B66+C66*(A67-A66)</f>
-        <v>2.40558559169841</v>
+        <v>-1.59441440830159</v>
       </c>
       <c r="C67" s="2" t="n">
         <f aca="false">A67^2*EXP(-A67)-1</f>
@@ -8565,7 +10092,7 @@
       </c>
       <c r="B68" s="2" t="n">
         <f aca="false">B67+C67*(A68-A67)</f>
-        <v>2.39779123510523</v>
+        <v>-1.60220876489478</v>
       </c>
       <c r="C68" s="2" t="n">
         <f aca="false">A68^2*EXP(-A68)-1</f>
@@ -8578,7 +10105,7 @@
       </c>
       <c r="B69" s="2" t="n">
         <f aca="false">B68+C68*(A69-A68)</f>
-        <v>2.39004263951827</v>
+        <v>-1.60995736048173</v>
       </c>
       <c r="C69" s="2" t="n">
         <f aca="false">A69^2*EXP(-A69)-1</f>
@@ -8591,7 +10118,7 @@
       </c>
       <c r="B70" s="2" t="n">
         <f aca="false">B69+C69*(A70-A69)</f>
-        <v>2.38233969932396</v>
+        <v>-1.61766030067605</v>
       </c>
       <c r="C70" s="2" t="n">
         <f aca="false">A70^2*EXP(-A70)-1</f>
@@ -8604,7 +10131,7 @@
       </c>
       <c r="B71" s="2" t="n">
         <f aca="false">B70+C70*(A71-A70)</f>
-        <v>2.37468229629665</v>
+        <v>-1.62531770370335</v>
       </c>
       <c r="C71" s="2" t="n">
         <f aca="false">A71^2*EXP(-A71)-1</f>
@@ -8617,7 +10144,7 @@
       </c>
       <c r="B72" s="2" t="n">
         <f aca="false">B71+C71*(A72-A71)</f>
-        <v>2.36707029996148</v>
+        <v>-1.63292970003852</v>
       </c>
       <c r="C72" s="2" t="n">
         <f aca="false">A72^2*EXP(-A72)-1</f>
@@ -8630,7 +10157,7 @@
       </c>
       <c r="B73" s="2" t="n">
         <f aca="false">B72+C72*(A73-A72)</f>
-        <v>2.35950356795006</v>
+        <v>-1.64049643204995</v>
       </c>
       <c r="C73" s="2" t="n">
         <f aca="false">A73^2*EXP(-A73)-1</f>
@@ -8643,7 +10170,7 @@
       </c>
       <c r="B74" s="2" t="n">
         <f aca="false">B73+C73*(A74-A73)</f>
-        <v>2.35198194634946</v>
+        <v>-1.64801805365054</v>
       </c>
       <c r="C74" s="2" t="n">
         <f aca="false">A74^2*EXP(-A74)-1</f>
@@ -8656,7 +10183,7 @@
       </c>
       <c r="B75" s="2" t="n">
         <f aca="false">B74+C74*(A75-A74)</f>
-        <v>2.34450527004435</v>
+        <v>-1.65549472995565</v>
       </c>
       <c r="C75" s="2" t="n">
         <f aca="false">A75^2*EXP(-A75)-1</f>
@@ -8669,7 +10196,7 @@
       </c>
       <c r="B76" s="2" t="n">
         <f aca="false">B75+C75*(A76-A75)</f>
-        <v>2.33707336305254</v>
+        <v>-1.66292663694746</v>
       </c>
       <c r="C76" s="2" t="n">
         <f aca="false">A76^2*EXP(-A76)-1</f>
@@ -8682,7 +10209,7 @@
       </c>
       <c r="B77" s="2" t="n">
         <f aca="false">B76+C76*(A77-A76)</f>
-        <v>2.32968603885394</v>
+        <v>-1.67031396114606</v>
       </c>
       <c r="C77" s="2" t="n">
         <f aca="false">A77^2*EXP(-A77)-1</f>
@@ -8695,7 +10222,7 @@
       </c>
       <c r="B78" s="2" t="n">
         <f aca="false">B77+C77*(A78-A77)</f>
-        <v>2.32234310071311</v>
+        <v>-1.6776568992869</v>
       </c>
       <c r="C78" s="2" t="n">
         <f aca="false">A78^2*EXP(-A78)-1</f>
@@ -8708,7 +10235,7 @@
       </c>
       <c r="B79" s="2" t="n">
         <f aca="false">B78+C78*(A79-A78)</f>
-        <v>2.31504434199552</v>
+        <v>-1.68495565800449</v>
       </c>
       <c r="C79" s="2" t="n">
         <f aca="false">A79^2*EXP(-A79)-1</f>
@@ -8721,7 +10248,7 @@
       </c>
       <c r="B80" s="2" t="n">
         <f aca="false">B79+C79*(A80-A79)</f>
-        <v>2.30778954647753</v>
+        <v>-1.69221045352247</v>
       </c>
       <c r="C80" s="2" t="n">
         <f aca="false">A80^2*EXP(-A80)-1</f>
@@ -8734,7 +10261,7 @@
       </c>
       <c r="B81" s="2" t="n">
         <f aca="false">B80+C80*(A81-A80)</f>
-        <v>2.30057848865031</v>
+        <v>-1.69942151134969</v>
       </c>
       <c r="C81" s="2" t="n">
         <f aca="false">A81^2*EXP(-A81)-1</f>
@@ -8747,7 +10274,7 @@
       </c>
       <c r="B82" s="2" t="n">
         <f aca="false">B81+C81*(A82-A81)</f>
-        <v>2.29341093401767</v>
+        <v>-1.70658906598233</v>
       </c>
       <c r="C82" s="2" t="n">
         <f aca="false">A82^2*EXP(-A82)-1</f>
@@ -8760,7 +10287,7 @@
       </c>
       <c r="B83" s="2" t="n">
         <f aca="false">B82+C82*(A83-A82)</f>
-        <v>2.28628663938802</v>
+        <v>-1.71371336061198</v>
       </c>
       <c r="C83" s="2" t="n">
         <f aca="false">A83^2*EXP(-A83)-1</f>
@@ -8773,7 +10300,7 @@
       </c>
       <c r="B84" s="2" t="n">
         <f aca="false">B83+C83*(A84-A83)</f>
-        <v>2.27920535316051</v>
+        <v>-1.72079464683949</v>
       </c>
       <c r="C84" s="2" t="n">
         <f aca="false">A84^2*EXP(-A84)-1</f>
@@ -8786,7 +10313,7 @@
       </c>
       <c r="B85" s="2" t="n">
         <f aca="false">B84+C84*(A85-A84)</f>
-        <v>2.27216681560541</v>
+        <v>-1.72783318439459</v>
       </c>
       <c r="C85" s="2" t="n">
         <f aca="false">A85^2*EXP(-A85)-1</f>
@@ -8799,7 +10326,7 @@
       </c>
       <c r="B86" s="2" t="n">
         <f aca="false">B85+C85*(A86-A85)</f>
-        <v>2.26517075913888</v>
+        <v>-1.73482924086113</v>
       </c>
       <c r="C86" s="2" t="n">
         <f aca="false">A86^2*EXP(-A86)-1</f>
@@ -8812,7 +10339,7 @@
       </c>
       <c r="B87" s="2" t="n">
         <f aca="false">B86+C86*(A87-A86)</f>
-        <v>2.25821690859219</v>
+        <v>-1.74178309140781</v>
       </c>
       <c r="C87" s="2" t="n">
         <f aca="false">A87^2*EXP(-A87)-1</f>
@@ -8825,7 +10352,7 @@
       </c>
       <c r="B88" s="2" t="n">
         <f aca="false">B87+C87*(A88-A87)</f>
-        <v>2.25130498147552</v>
+        <v>-1.74869501852448</v>
       </c>
       <c r="C88" s="2" t="n">
         <f aca="false">A88^2*EXP(-A88)-1</f>
@@ -8838,7 +10365,7 @@
       </c>
       <c r="B89" s="2" t="n">
         <f aca="false">B88+C88*(A89-A88)</f>
-        <v>2.24443468823634</v>
+        <v>-1.75556531176366</v>
       </c>
       <c r="C89" s="2" t="n">
         <f aca="false">A89^2*EXP(-A89)-1</f>
@@ -8851,7 +10378,7 @@
       </c>
       <c r="B90" s="2" t="n">
         <f aca="false">B89+C89*(A90-A89)</f>
-        <v>2.2376057325126</v>
+        <v>-1.7623942674874</v>
       </c>
       <c r="C90" s="2" t="n">
         <f aca="false">A90^2*EXP(-A90)-1</f>
@@ -8864,7 +10391,7 @@
       </c>
       <c r="B91" s="2" t="n">
         <f aca="false">B90+C90*(A91-A90)</f>
-        <v>2.23081781138066</v>
+        <v>-1.76918218861934</v>
       </c>
       <c r="C91" s="2" t="n">
         <f aca="false">A91^2*EXP(-A91)-1</f>
@@ -8877,7 +10404,7 @@
       </c>
       <c r="B92" s="2" t="n">
         <f aca="false">B91+C91*(A92-A91)</f>
-        <v>2.22407061559821</v>
+        <v>-1.77592938440179</v>
       </c>
       <c r="C92" s="2" t="n">
         <f aca="false">A92^2*EXP(-A92)-1</f>
@@ -8890,7 +10417,7 @@
       </c>
       <c r="B93" s="2" t="n">
         <f aca="false">B92+C92*(A93-A92)</f>
-        <v>2.21736382984211</v>
+        <v>-1.78263617015789</v>
       </c>
       <c r="C93" s="2" t="n">
         <f aca="false">A93^2*EXP(-A93)-1</f>
@@ -8903,7 +10430,7 @@
       </c>
       <c r="B94" s="2" t="n">
         <f aca="false">B93+C93*(A94-A93)</f>
-        <v>2.21069713294133</v>
+        <v>-1.78930286705867</v>
       </c>
       <c r="C94" s="2" t="n">
         <f aca="false">A94^2*EXP(-A94)-1</f>
@@ -8916,7 +10443,7 @@
       </c>
       <c r="B95" s="2" t="n">
         <f aca="false">B94+C94*(A95-A94)</f>
-        <v>2.20407019810507</v>
+        <v>-1.79592980189493</v>
       </c>
       <c r="C95" s="2" t="n">
         <f aca="false">A95^2*EXP(-A95)-1</f>
@@ -8929,7 +10456,7 @@
       </c>
       <c r="B96" s="2" t="n">
         <f aca="false">B95+C95*(A96-A95)</f>
-        <v>2.19748269314608</v>
+        <v>-1.80251730685392</v>
       </c>
       <c r="C96" s="2" t="n">
         <f aca="false">A96^2*EXP(-A96)-1</f>
@@ -8942,7 +10469,7 @@
       </c>
       <c r="B97" s="2" t="n">
         <f aca="false">B96+C96*(A97-A96)</f>
-        <v>2.1909342806993</v>
+        <v>-1.8090657193007</v>
       </c>
       <c r="C97" s="2" t="n">
         <f aca="false">A97^2*EXP(-A97)-1</f>
@@ -8955,7 +10482,7 @@
       </c>
       <c r="B98" s="2" t="n">
         <f aca="false">B97+C97*(A98-A97)</f>
-        <v>2.18442461843598</v>
+        <v>-1.81557538156402</v>
       </c>
       <c r="C98" s="2" t="n">
         <f aca="false">A98^2*EXP(-A98)-1</f>
@@ -8968,7 +10495,7 @@
       </c>
       <c r="B99" s="2" t="n">
         <f aca="false">B98+C98*(A99-A98)</f>
-        <v>2.17795335927313</v>
+        <v>-1.82204664072687</v>
       </c>
       <c r="C99" s="2" t="n">
         <f aca="false">A99^2*EXP(-A99)-1</f>
@@ -8981,7 +10508,7 @@
       </c>
       <c r="B100" s="2" t="n">
         <f aca="false">B99+C99*(A100-A99)</f>
-        <v>2.17152015157864</v>
+        <v>-1.82847984842136</v>
       </c>
       <c r="C100" s="2" t="n">
         <f aca="false">A100^2*EXP(-A100)-1</f>
@@ -8994,7 +10521,7 @@
       </c>
       <c r="B101" s="2" t="n">
         <f aca="false">B100+C100*(A101-A100)</f>
-        <v>2.16512463937201</v>
+        <v>-1.83487536062799</v>
       </c>
       <c r="C101" s="2" t="n">
         <f aca="false">A101^2*EXP(-A101)-1</f>
@@ -9007,7 +10534,7 @@
       </c>
       <c r="B102" s="2" t="n">
         <f aca="false">B101+C101*(A102-A101)</f>
-        <v>2.15876646252072</v>
+        <v>-1.84123353747928</v>
       </c>
       <c r="C102" s="2" t="n">
         <f aca="false">A102^2*EXP(-A102)-1</f>
@@ -9020,7 +10547,7 @@
       </c>
       <c r="B103" s="2" t="n">
         <f aca="false">B102+C102*(A103-A102)</f>
-        <v>2.15244525693243</v>
+        <v>-1.84755474306757</v>
       </c>
       <c r="C103" s="2" t="n">
         <f aca="false">A103^2*EXP(-A103)-1</f>
@@ -9033,7 +10560,7 @@
       </c>
       <c r="B104" s="2" t="n">
         <f aca="false">B103+C103*(A104-A103)</f>
-        <v>2.14616065474304</v>
+        <v>-1.85383934525696</v>
       </c>
       <c r="C104" s="2" t="n">
         <f aca="false">A104^2*EXP(-A104)-1</f>
@@ -9046,7 +10573,7 @@
       </c>
       <c r="B105" s="2" t="n">
         <f aca="false">B104+C104*(A105-A104)</f>
-        <v>2.1399122845006</v>
+        <v>-1.8600877154994</v>
       </c>
       <c r="C105" s="2" t="n">
         <f aca="false">A105^2*EXP(-A105)-1</f>
@@ -9059,7 +10586,7 @@
       </c>
       <c r="B106" s="2" t="n">
         <f aca="false">B105+C105*(A106-A105)</f>
-        <v>2.13369977134528</v>
+        <v>-1.86630022865472</v>
       </c>
       <c r="C106" s="2" t="n">
         <f aca="false">A106^2*EXP(-A106)-1</f>
@@ -9072,7 +10599,7 @@
       </c>
       <c r="B107" s="2" t="n">
         <f aca="false">B106+C106*(A107-A106)</f>
-        <v>2.12752273718535</v>
+        <v>-1.87247726281465</v>
       </c>
       <c r="C107" s="2" t="n">
         <f aca="false">A107^2*EXP(-A107)-1</f>
@@ -9085,7 +10612,7 @@
       </c>
       <c r="B108" s="2" t="n">
         <f aca="false">B107+C107*(A108-A107)</f>
-        <v>2.1213808008693</v>
+        <v>-1.8786191991307</v>
       </c>
       <c r="C108" s="2" t="n">
         <f aca="false">A108^2*EXP(-A108)-1</f>
@@ -9098,7 +10625,7 @@
       </c>
       <c r="B109" s="2" t="n">
         <f aca="false">B108+C108*(A109-A108)</f>
-        <v>2.11527357835417</v>
+        <v>-1.88472642164584</v>
       </c>
       <c r="C109" s="2" t="n">
         <f aca="false">A109^2*EXP(-A109)-1</f>
@@ -9111,7 +10638,7 @@
       </c>
       <c r="B110" s="2" t="n">
         <f aca="false">B109+C109*(A110-A109)</f>
-        <v>2.10920068287009</v>
+        <v>-1.89079931712991</v>
       </c>
       <c r="C110" s="2" t="n">
         <f aca="false">A110^2*EXP(-A110)-1</f>
@@ -9124,7 +10651,7 @@
       </c>
       <c r="B111" s="2" t="n">
         <f aca="false">B110+C110*(A111-A110)</f>
-        <v>2.10316172508122</v>
+        <v>-1.89683827491879</v>
       </c>
       <c r="C111" s="2" t="n">
         <f aca="false">A111^2*EXP(-A111)-1</f>
@@ -9137,7 +10664,7 @@
       </c>
       <c r="B112" s="2" t="n">
         <f aca="false">B111+C111*(A112-A111)</f>
-        <v>2.09715631324295</v>
+        <v>-1.90284368675706</v>
       </c>
       <c r="C112" s="2" t="n">
         <f aca="false">A112^2*EXP(-A112)-1</f>
@@ -9150,7 +10677,7 @@
       </c>
       <c r="B113" s="2" t="n">
         <f aca="false">B112+C112*(A113-A112)</f>
-        <v>2.09118405335569</v>
+        <v>-1.90881594664431</v>
       </c>
       <c r="C113" s="2" t="n">
         <f aca="false">A113^2*EXP(-A113)-1</f>
@@ -9163,7 +10690,7 @@
       </c>
       <c r="B114" s="2" t="n">
         <f aca="false">B113+C113*(A114-A113)</f>
-        <v>2.0852445493151</v>
+        <v>-1.9147554506849</v>
       </c>
       <c r="C114" s="2" t="n">
         <f aca="false">A114^2*EXP(-A114)-1</f>
@@ -9176,7 +10703,7 @@
       </c>
       <c r="B115" s="2" t="n">
         <f aca="false">B114+C114*(A115-A114)</f>
-        <v>2.07933740305885</v>
+        <v>-1.92066259694115</v>
       </c>
       <c r="C115" s="2" t="n">
         <f aca="false">A115^2*EXP(-A115)-1</f>
@@ -9189,7 +10716,7 @@
       </c>
       <c r="B116" s="2" t="n">
         <f aca="false">B115+C115*(A116-A115)</f>
-        <v>2.07346221471011</v>
+        <v>-1.92653778528989</v>
       </c>
       <c r="C116" s="2" t="n">
         <f aca="false">A116^2*EXP(-A116)-1</f>
@@ -9202,7 +10729,7 @@
       </c>
       <c r="B117" s="2" t="n">
         <f aca="false">B116+C116*(A117-A116)</f>
-        <v>2.06761858271763</v>
+        <v>-1.93238141728237</v>
       </c>
       <c r="C117" s="2" t="n">
         <f aca="false">A117^2*EXP(-A117)-1</f>
@@ -9215,7 +10742,7 @@
       </c>
       <c r="B118" s="2" t="n">
         <f aca="false">B117+C117*(A118-A117)</f>
-        <v>2.06180610399267</v>
+        <v>-1.93819389600733</v>
       </c>
       <c r="C118" s="2" t="n">
         <f aca="false">A118^2*EXP(-A118)-1</f>
@@ -9228,7 +10755,7 @@
       </c>
       <c r="B119" s="2" t="n">
         <f aca="false">B118+C118*(A119-A118)</f>
-        <v>2.05602437404263</v>
+        <v>-1.94397562595738</v>
       </c>
       <c r="C119" s="2" t="n">
         <f aca="false">A119^2*EXP(-A119)-1</f>
@@ -9241,7 +10768,7 @@
       </c>
       <c r="B120" s="2" t="n">
         <f aca="false">B119+C119*(A120-A119)</f>
-        <v>2.05027298710161</v>
+        <v>-1.94972701289839</v>
       </c>
       <c r="C120" s="2" t="n">
         <f aca="false">A120^2*EXP(-A120)-1</f>
@@ -9254,7 +10781,7 @@
       </c>
       <c r="B121" s="2" t="n">
         <f aca="false">B120+C120*(A121-A120)</f>
-        <v>2.04455153625789</v>
+        <v>-1.95544846374211</v>
       </c>
       <c r="C121" s="2" t="n">
         <f aca="false">A121^2*EXP(-A121)-1</f>
@@ -9267,7 +10794,7 @@
       </c>
       <c r="B122" s="2" t="n">
         <f aca="false">B121+C121*(A122-A121)</f>
-        <v>2.03885961357834</v>
+        <v>-1.96114038642166</v>
       </c>
       <c r="C122" s="2" t="n">
         <f aca="false">A122^2*EXP(-A122)-1</f>
@@ -9280,7 +10807,7 @@
       </c>
       <c r="B123" s="2" t="n">
         <f aca="false">B122+C122*(A123-A122)</f>
-        <v>2.03319681022988</v>
+        <v>-1.96680318977013</v>
       </c>
       <c r="C123" s="2" t="n">
         <f aca="false">A123^2*EXP(-A123)-1</f>
@@ -9293,7 +10820,7 @@
       </c>
       <c r="B124" s="2" t="n">
         <f aca="false">B123+C123*(A124-A123)</f>
-        <v>2.02756271659801</v>
+        <v>-1.97243728340199</v>
       </c>
       <c r="C124" s="2" t="n">
         <f aca="false">A124^2*EXP(-A124)-1</f>
@@ -9306,7 +10833,7 @@
       </c>
       <c r="B125" s="2" t="n">
         <f aca="false">B124+C124*(A125-A124)</f>
-        <v>2.02195692240251</v>
+        <v>-1.9780430775975</v>
       </c>
       <c r="C125" s="2" t="n">
         <f aca="false">A125^2*EXP(-A125)-1</f>
@@ -9319,7 +10846,7 @@
       </c>
       <c r="B126" s="2" t="n">
         <f aca="false">B125+C125*(A126-A125)</f>
-        <v>2.01637901681024</v>
+        <v>-1.98362098318976</v>
       </c>
       <c r="C126" s="2" t="n">
         <f aca="false">A126^2*EXP(-A126)-1</f>
@@ -9401,7 +10928,7 @@
       </c>
       <c r="E3" s="2" t="n">
         <f aca="false">(D3-B3)/D3*100</f>
-        <v>0.00503345866736856</v>
+        <v>0.00503345866735735</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9422,7 +10949,7 @@
       </c>
       <c r="E4" s="2" t="n">
         <f aca="false">(D4-B4)/D4*100</f>
-        <v>0.0100666639776609</v>
+        <v>0.0100666639776383</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9443,7 +10970,7 @@
       </c>
       <c r="E5" s="2" t="n">
         <f aca="false">(D5-B5)/D5*100</f>
-        <v>0.0150996159436502</v>
+        <v>0.0150996159436388</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9464,7 +10991,7 @@
       </c>
       <c r="E6" s="2" t="n">
         <f aca="false">(D6-B6)/D6*100</f>
-        <v>0.0201323145780805</v>
+        <v>0.0201323145780574</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9506,7 +11033,7 @@
       </c>
       <c r="E8" s="2" t="n">
         <f aca="false">(D8-B8)/D8*100</f>
-        <v>0.0301969519032944</v>
+        <v>0.0301969519033298</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9527,7 +11054,7 @@
       </c>
       <c r="E9" s="2" t="n">
         <f aca="false">(D9-B9)/D9*100</f>
-        <v>0.0352288906195646</v>
+        <v>0.0352288906195408</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9548,7 +11075,7 @@
       </c>
       <c r="E10" s="2" t="n">
         <f aca="false">(D10-B10)/D10*100</f>
-        <v>0.0402605760552655</v>
+        <v>0.0402605760552896</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9569,7 +11096,7 @@
       </c>
       <c r="E11" s="2" t="n">
         <f aca="false">(D11-B11)/D11*100</f>
-        <v>0.0452920082231797</v>
+        <v>0.0452920082231554</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9590,7 +11117,7 @@
       </c>
       <c r="E12" s="2" t="n">
         <f aca="false">(D12-B12)/D12*100</f>
-        <v>0.0503231871360233</v>
+        <v>0.0503231871360724</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9611,7 +11138,7 @@
       </c>
       <c r="E13" s="2" t="n">
         <f aca="false">(D13-B13)/D13*100</f>
-        <v>0.055354112806562</v>
+        <v>0.0553541128065372</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9632,7 +11159,7 @@
       </c>
       <c r="E14" s="2" t="n">
         <f aca="false">(D14-B14)/D14*100</f>
-        <v>0.060384785247533</v>
+        <v>0.0603847852475956</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9653,7 +11180,7 @@
       </c>
       <c r="E15" s="2" t="n">
         <f aca="false">(D15-B15)/D15*100</f>
-        <v>0.0654152044716892</v>
+        <v>0.0654152044716513</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9674,7 +11201,7 @@
       </c>
       <c r="E16" s="2" t="n">
         <f aca="false">(D16-B16)/D16*100</f>
-        <v>0.070445370491784</v>
+        <v>0.0704453704917968</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9695,7 +11222,7 @@
       </c>
       <c r="E17" s="2" t="n">
         <f aca="false">(D17-B17)/D17*100</f>
-        <v>0.0754752833205356</v>
+        <v>0.0754752833205614</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9716,7 +11243,7 @@
       </c>
       <c r="E18" s="2" t="n">
         <f aca="false">(D18-B18)/D18*100</f>
-        <v>0.0805049429707116</v>
+        <v>0.0805049429706725</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9737,7 +11264,7 @@
       </c>
       <c r="E19" s="2" t="n">
         <f aca="false">(D19-B19)/D19*100</f>
-        <v>0.0855343494550473</v>
+        <v>0.0855343494550867</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9779,7 +11306,7 @@
       </c>
       <c r="E21" s="2" t="n">
         <f aca="false">(D21-B21)/D21*100</f>
-        <v>0.0955924029771554</v>
+        <v>0.0955924029771151</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9800,7 +11327,7 @@
       </c>
       <c r="E22" s="2" t="n">
         <f aca="false">(D22-B22)/D22*100</f>
-        <v>0.100621050040425</v>
+        <v>0.100621050040452</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9821,7 +11348,7 @@
       </c>
       <c r="E23" s="2" t="n">
         <f aca="false">(D23-B23)/D23*100</f>
-        <v>0.10564944398883</v>
+        <v>0.105649443988816</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9842,7 +11369,7 @@
       </c>
       <c r="E24" s="2" t="n">
         <f aca="false">(D24-B24)/D24*100</f>
-        <v>0.110677584835096</v>
+        <v>0.110677584835165</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9884,7 +11411,7 @@
       </c>
       <c r="E26" s="2" t="n">
         <f aca="false">(D26-B26)/D26*100</f>
-        <v>0.120733107272199</v>
+        <v>0.120733107272269</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9905,7 +11432,7 @@
       </c>
       <c r="E27" s="2" t="n">
         <f aca="false">(D27-B27)/D27*100</f>
-        <v>0.125760488888507</v>
+        <v>0.125760488888521</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9926,7 +11453,7 @@
       </c>
       <c r="E28" s="2" t="n">
         <f aca="false">(D28-B28)/D28*100</f>
-        <v>0.130787617453633</v>
+        <v>0.130787617453604</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9947,7 +11474,7 @@
       </c>
       <c r="E29" s="2" t="n">
         <f aca="false">(D29-B29)/D29*100</f>
-        <v>0.135814492980327</v>
+        <v>0.135814492980312</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9968,7 +11495,7 @@
       </c>
       <c r="E30" s="2" t="n">
         <f aca="false">(D30-B30)/D30*100</f>
-        <v>0.140841115481331</v>
+        <v>0.140841115481405</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9989,7 +11516,7 @@
       </c>
       <c r="E31" s="2" t="n">
         <f aca="false">(D31-B31)/D31*100</f>
-        <v>0.145867484969365</v>
+        <v>0.145867484969336</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10010,7 +11537,7 @@
       </c>
       <c r="E32" s="2" t="n">
         <f aca="false">(D32-B32)/D32*100</f>
-        <v>0.150893601457153</v>
+        <v>0.150893601457168</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10031,7 +11558,7 @@
       </c>
       <c r="E33" s="2" t="n">
         <f aca="false">(D33-B33)/D33*100</f>
-        <v>0.155919464957457</v>
+        <v>0.155919464957426</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10052,7 +11579,7 @@
       </c>
       <c r="E34" s="2" t="n">
         <f aca="false">(D34-B34)/D34*100</f>
-        <v>0.160945075483001</v>
+        <v>0.160945075483016</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10073,7 +11600,7 @@
       </c>
       <c r="E35" s="2" t="n">
         <f aca="false">(D35-B35)/D35*100</f>
-        <v>0.165970433046517</v>
+        <v>0.165970433046486</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10094,7 +11621,7 @@
       </c>
       <c r="E36" s="2" t="n">
         <f aca="false">(D36-B36)/D36*100</f>
-        <v>0.170995537660717</v>
+        <v>0.170995537660764</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10115,7 +11642,7 @@
       </c>
       <c r="E37" s="2" t="n">
         <f aca="false">(D37-B37)/D37*100</f>
-        <v>0.176020389338378</v>
+        <v>0.176020389338315</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10157,7 +11684,7 @@
       </c>
       <c r="E39" s="2" t="n">
         <f aca="false">(D39-B39)/D39*100</f>
-        <v>0.186069333934918</v>
+        <v>0.186069333934966</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10178,7 +11705,7 @@
       </c>
       <c r="E40" s="2" t="n">
         <f aca="false">(D40-B40)/D40*100</f>
-        <v>0.191093426879255</v>
+        <v>0.191093426879287</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10199,7 +11726,7 @@
       </c>
       <c r="E41" s="2" t="n">
         <f aca="false">(D41-B41)/D41*100</f>
-        <v>0.196117266937956</v>
+        <v>0.196117266938005</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10220,7 +11747,7 @@
       </c>
       <c r="E42" s="2" t="n">
         <f aca="false">(D42-B42)/D42*100</f>
-        <v>0.201140854123755</v>
+        <v>0.201140854123705</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10241,7 +11768,7 @@
       </c>
       <c r="E43" s="2" t="n">
         <f aca="false">(D43-B43)/D43*100</f>
-        <v>0.206164188449363</v>
+        <v>0.206164188449296</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10262,7 +11789,7 @@
       </c>
       <c r="E44" s="2" t="n">
         <f aca="false">(D44-B44)/D44*100</f>
-        <v>0.211187269927506</v>
+        <v>0.21118726992754</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10283,7 +11810,7 @@
       </c>
       <c r="E45" s="2" t="n">
         <f aca="false">(D45-B45)/D45*100</f>
-        <v>0.21621009857093</v>
+        <v>0.216210098570998</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10304,7 +11831,7 @@
       </c>
       <c r="E46" s="2" t="n">
         <f aca="false">(D46-B46)/D46*100</f>
-        <v>0.221232674392358</v>
+        <v>0.221232674392289</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10325,7 +11852,7 @@
       </c>
       <c r="E47" s="2" t="n">
         <f aca="false">(D47-B47)/D47*100</f>
-        <v>0.226254997404496</v>
+        <v>0.226254997404444</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10367,7 +11894,7 @@
       </c>
       <c r="E49" s="2" t="n">
         <f aca="false">(D49-B49)/D49*100</f>
-        <v>0.236298885051819</v>
+        <v>0.236298885051854</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10388,7 +11915,7 @@
       </c>
       <c r="E50" s="2" t="n">
         <f aca="false">(D50-B50)/D50*100</f>
-        <v>0.241320449712471</v>
+        <v>0.241320449712488</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10409,7 +11936,7 @@
       </c>
       <c r="E51" s="2" t="n">
         <f aca="false">(D51-B51)/D51*100</f>
-        <v>0.246341761614743</v>
+        <v>0.246341761614725</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10430,7 +11957,7 @@
       </c>
       <c r="E52" s="2" t="n">
         <f aca="false">(D52-B52)/D52*100</f>
-        <v>0.251362820771348</v>
+        <v>0.251362820771275</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10451,7 +11978,7 @@
       </c>
       <c r="E53" s="2" t="n">
         <f aca="false">(D53-B53)/D53*100</f>
-        <v>0.256383627195014</v>
+        <v>0.256383627195032</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10472,7 +11999,7 @@
       </c>
       <c r="E54" s="2" t="n">
         <f aca="false">(D54-B54)/D54*100</f>
-        <v>0.261404180898495</v>
+        <v>0.261404180898439</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10493,7 +12020,7 @@
       </c>
       <c r="E55" s="2" t="n">
         <f aca="false">(D55-B55)/D55*100</f>
-        <v>0.266424481894448</v>
+        <v>0.26642448189441</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10514,7 +12041,7 @@
       </c>
       <c r="E56" s="2" t="n">
         <f aca="false">(D56-B56)/D56*100</f>
-        <v>0.271444530195639</v>
+        <v>0.271444530195696</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10535,7 +12062,7 @@
       </c>
       <c r="E57" s="2" t="n">
         <f aca="false">(D57-B57)/D57*100</f>
-        <v>0.27646432581476</v>
+        <v>0.276464325814817</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10556,7 +12083,7 @@
       </c>
       <c r="E58" s="2" t="n">
         <f aca="false">(D58-B58)/D58*100</f>
-        <v>0.28148386876456</v>
+        <v>0.28148386876458</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10577,7 +12104,7 @@
       </c>
       <c r="E59" s="2" t="n">
         <f aca="false">(D59-B59)/D59*100</f>
-        <v>0.286503159057726</v>
+        <v>0.286503159057706</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10619,7 +12146,7 @@
       </c>
       <c r="E61" s="2" t="n">
         <f aca="false">(D61-B61)/D61*100</f>
-        <v>0.296540981725099</v>
+        <v>0.296540981725079</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10640,7 +12167,7 @@
       </c>
       <c r="E62" s="2" t="n">
         <f aca="false">(D62-B62)/D62*100</f>
-        <v>0.301559514124696</v>
+        <v>0.301559514124615</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10661,7 +12188,7 @@
       </c>
       <c r="E63" s="2" t="n">
         <f aca="false">(D63-B63)/D63*100</f>
-        <v>0.306577793918579</v>
+        <v>0.30657779391862</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10682,7 +12209,7 @@
       </c>
       <c r="E64" s="2" t="n">
         <f aca="false">(D64-B64)/D64*100</f>
-        <v>0.311595821119402</v>
+        <v>0.311595821119505</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10703,7 +12230,7 @@
       </c>
       <c r="E65" s="2" t="n">
         <f aca="false">(D65-B65)/D65*100</f>
-        <v>0.316613595739894</v>
+        <v>0.316613595739852</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10724,7 +12251,7 @@
       </c>
       <c r="E66" s="2" t="n">
         <f aca="false">(D66-B66)/D66*100</f>
-        <v>0.321631117792787</v>
+        <v>0.321631117792871</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10766,7 +12293,7 @@
       </c>
       <c r="E68" s="2" t="n">
         <f aca="false">(D68-B68)/D68*100</f>
-        <v>0.331665404246563</v>
+        <v>0.331665404246521</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10787,7 +12314,7 @@
       </c>
       <c r="E69" s="2" t="n">
         <f aca="false">(D69-B69)/D69*100</f>
-        <v>0.336682168672892</v>
+        <v>0.336682168672805</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10808,7 +12335,7 @@
       </c>
       <c r="E70" s="2" t="n">
         <f aca="false">(D70-B70)/D70*100</f>
-        <v>0.341698680582446</v>
+        <v>0.341698680582533</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10829,7 +12356,7 @@
       </c>
       <c r="E71" s="2" t="n">
         <f aca="false">(D71-B71)/D71*100</f>
-        <v>0.346714939987963</v>
+        <v>0.346714939988052</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10850,7 +12377,7 @@
       </c>
       <c r="E72" s="2" t="n">
         <f aca="false">(D72-B72)/D72*100</f>
-        <v>0.35173094690212</v>
+        <v>0.351730946902221</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10871,7 +12398,7 @@
       </c>
       <c r="E73" s="2" t="n">
         <f aca="false">(D73-B73)/D73*100</f>
-        <v>0.356746701337644</v>
+        <v>0.356746701337621</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10892,7 +12419,7 @@
       </c>
       <c r="E74" s="2" t="n">
         <f aca="false">(D74-B74)/D74*100</f>
-        <v>0.361762203307256</v>
+        <v>0.361762203307324</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10913,7 +12440,7 @@
       </c>
       <c r="E75" s="2" t="n">
         <f aca="false">(D75-B75)/D75*100</f>
-        <v>0.366777452823636</v>
+        <v>0.366777452823544</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10934,7 +12461,7 @@
       </c>
       <c r="E76" s="2" t="n">
         <f aca="false">(D76-B76)/D76*100</f>
-        <v>0.371792449899502</v>
+        <v>0.371792449899421</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10955,7 +12482,7 @@
       </c>
       <c r="E77" s="2" t="n">
         <f aca="false">(D77-B77)/D77*100</f>
-        <v>0.376807194547566</v>
+        <v>0.376807194547636</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10976,7 +12503,7 @@
       </c>
       <c r="E78" s="2" t="n">
         <f aca="false">(D78-B78)/D78*100</f>
-        <v>0.381821686780543</v>
+        <v>0.381821686780496</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10997,7 +12524,7 @@
       </c>
       <c r="E79" s="2" t="n">
         <f aca="false">(D79-B79)/D79*100</f>
-        <v>0.386835926611124</v>
+        <v>0.386835926611112</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11018,7 +12545,7 @@
       </c>
       <c r="E80" s="2" t="n">
         <f aca="false">(D80-B80)/D80*100</f>
-        <v>0.391849914052005</v>
+        <v>0.391849914052113</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11039,7 +12566,7 @@
       </c>
       <c r="E81" s="2" t="n">
         <f aca="false">(D81-B81)/D81*100</f>
-        <v>0.39686364911591</v>
+        <v>0.396863649115947</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11060,7 +12587,7 @@
       </c>
       <c r="E82" s="2" t="n">
         <f aca="false">(D82-B82)/D82*100</f>
-        <v>0.401877131815522</v>
+        <v>0.40187713181562</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11081,7 +12608,7 @@
       </c>
       <c r="E83" s="2" t="n">
         <f aca="false">(D83-B83)/D83*100</f>
-        <v>0.406890362163563</v>
+        <v>0.406890362163538</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11102,7 +12629,7 @@
       </c>
       <c r="E84" s="2" t="n">
         <f aca="false">(D84-B84)/D84*100</f>
-        <v>0.411903340172723</v>
+        <v>0.411903340172661</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11123,7 +12650,7 @@
       </c>
       <c r="E85" s="2" t="n">
         <f aca="false">(D85-B85)/D85*100</f>
-        <v>0.416916065855707</v>
+        <v>0.416916065855796</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11144,7 +12671,7 @@
       </c>
       <c r="E86" s="2" t="n">
         <f aca="false">(D86-B86)/D86*100</f>
-        <v>0.421928539225221</v>
+        <v>0.421928539225285</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11165,7 +12692,7 @@
       </c>
       <c r="E87" s="2" t="n">
         <f aca="false">(D87-B87)/D87*100</f>
-        <v>0.426940760293954</v>
+        <v>0.426940760294018</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11186,7 +12713,7 @@
       </c>
       <c r="E88" s="2" t="n">
         <f aca="false">(D88-B88)/D88*100</f>
-        <v>0.4319527290746</v>
+        <v>0.431952729074639</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11228,7 +12755,7 @@
       </c>
       <c r="E90" s="2" t="n">
         <f aca="false">(D90-B90)/D90*100</f>
-        <v>0.441975909822482</v>
+        <v>0.441975909822388</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11249,7 +12776,7 @@
       </c>
       <c r="E91" s="2" t="n">
         <f aca="false">(D91-B91)/D91*100</f>
-        <v>0.446987121815105</v>
+        <v>0.446987121815226</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11270,7 +12797,7 @@
       </c>
       <c r="E92" s="2" t="n">
         <f aca="false">(D92-B92)/D92*100</f>
-        <v>0.451998081570432</v>
+        <v>0.451998081570405</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11291,7 +12818,7 @@
       </c>
       <c r="E93" s="2" t="n">
         <f aca="false">(D93-B93)/D93*100</f>
-        <v>0.457008789101179</v>
+        <v>0.457008789101193</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11312,7 +12839,7 @@
       </c>
       <c r="E94" s="2" t="n">
         <f aca="false">(D94-B94)/D94*100</f>
-        <v>0.462019244420036</v>
+        <v>0.462019244420008</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11333,7 +12860,7 @@
       </c>
       <c r="E95" s="2" t="n">
         <f aca="false">(D95-B95)/D95*100</f>
-        <v>0.46702944753969</v>
+        <v>0.467029447539662</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11354,7 +12881,7 @@
       </c>
       <c r="E96" s="2" t="n">
         <f aca="false">(D96-B96)/D96*100</f>
-        <v>0.472039398472854</v>
+        <v>0.472039398472826</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11375,7 +12902,7 @@
       </c>
       <c r="E97" s="2" t="n">
         <f aca="false">(D97-B97)/D97*100</f>
-        <v>0.477049097232195</v>
+        <v>0.477049097232138</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11396,7 +12923,7 @@
       </c>
       <c r="E98" s="2" t="n">
         <f aca="false">(D98-B98)/D98*100</f>
-        <v>0.482058543830435</v>
+        <v>0.482058543830421</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11417,7 +12944,7 @@
       </c>
       <c r="E99" s="2" t="n">
         <f aca="false">(D99-B99)/D99*100</f>
-        <v>0.487067738280232</v>
+        <v>0.487067738280275</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11438,7 +12965,7 @@
       </c>
       <c r="E100" s="2" t="n">
         <f aca="false">(D100-B100)/D100*100</f>
-        <v>0.492076680594317</v>
+        <v>0.492076680594435</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11459,7 +12986,7 @@
       </c>
       <c r="E101" s="2" t="n">
         <f aca="false">(D101-B101)/D101*100</f>
-        <v>0.497085370785354</v>
+        <v>0.497085370785428</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11480,7 +13007,7 @@
       </c>
       <c r="E102" s="2" t="n">
         <f aca="false">(D102-B102)/D102*100</f>
-        <v>0.502093808866041</v>
+        <v>0.502093808865951</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11501,7 +13028,7 @@
       </c>
       <c r="E103" s="2" t="n">
         <f aca="false">(D103-B103)/D103*100</f>
-        <v>0.507101994849066</v>
+        <v>0.507101994848975</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11522,7 +13049,7 @@
       </c>
       <c r="E104" s="2" t="n">
         <f aca="false">(D104-B104)/D104*100</f>
-        <v>0.512109928747113</v>
+        <v>0.512109928747036</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11543,7 +13070,7 @@
       </c>
       <c r="E105" s="2" t="n">
         <f aca="false">(D105-B105)/D105*100</f>
-        <v>0.517117610572885</v>
+        <v>0.517117610572777</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11564,7 +13091,7 @@
       </c>
       <c r="E106" s="2" t="n">
         <f aca="false">(D106-B106)/D106*100</f>
-        <v>0.522125040339061</v>
+        <v>0.522125040339014</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11585,7 +13112,7 @@
       </c>
       <c r="E107" s="2" t="n">
         <f aca="false">(D107-B107)/D107*100</f>
-        <v>0.527132218058317</v>
+        <v>0.527132218058222</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11606,7 +13133,7 @@
       </c>
       <c r="E108" s="2" t="n">
         <f aca="false">(D108-B108)/D108*100</f>
-        <v>0.532139143743359</v>
+        <v>0.532139143743247</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11627,7 +13154,7 @@
       </c>
       <c r="E109" s="2" t="n">
         <f aca="false">(D109-B109)/D109*100</f>
-        <v>0.537145817406877</v>
+        <v>0.537145817406989</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11648,7 +13175,7 @@
       </c>
       <c r="E110" s="2" t="n">
         <f aca="false">(D110-B110)/D110*100</f>
-        <v>0.542152239061532</v>
+        <v>0.542152239061499</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11669,7 +13196,7 @@
       </c>
       <c r="E111" s="2" t="n">
         <f aca="false">(D111-B111)/D111*100</f>
-        <v>0.547158408720044</v>
+        <v>0.547158408719946</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11690,7 +13217,7 @@
       </c>
       <c r="E112" s="2" t="n">
         <f aca="false">(D112-B112)/D112*100</f>
-        <v>0.552164326395054</v>
+        <v>0.552164326395186</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11711,7 +13238,7 @@
       </c>
       <c r="E113" s="2" t="n">
         <f aca="false">(D113-B113)/D113*100</f>
-        <v>0.557169992099271</v>
+        <v>0.557169992099254</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11732,7 +13259,7 @@
       </c>
       <c r="E114" s="2" t="n">
         <f aca="false">(D114-B114)/D114*100</f>
-        <v>0.56217540584537</v>
+        <v>0.562175405845235</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11753,7 +13280,7 @@
       </c>
       <c r="E115" s="2" t="n">
         <f aca="false">(D115-B115)/D115*100</f>
-        <v>0.567180567646034</v>
+        <v>0.567180567646051</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11774,7 +13301,7 @@
       </c>
       <c r="E116" s="2" t="n">
         <f aca="false">(D116-B116)/D116*100</f>
-        <v>0.57218547751397</v>
+        <v>0.572185477513987</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11795,7 +13322,7 @@
       </c>
       <c r="E117" s="2" t="n">
         <f aca="false">(D117-B117)/D117*100</f>
-        <v>0.577190135461827</v>
+        <v>0.57719013546174</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11816,7 +13343,7 @@
       </c>
       <c r="E118" s="2" t="n">
         <f aca="false">(D118-B118)/D118*100</f>
-        <v>0.582194541502278</v>
+        <v>0.582194541502172</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11837,7 +13364,7 @@
       </c>
       <c r="E119" s="2" t="n">
         <f aca="false">(D119-B119)/D119*100</f>
-        <v>0.587198695648034</v>
+        <v>0.587198695648016</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11858,7 +13385,7 @@
       </c>
       <c r="E120" s="2" t="n">
         <f aca="false">(D120-B120)/D120*100</f>
-        <v>0.592202597911758</v>
+        <v>0.592202597911668</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11879,7 +13406,7 @@
       </c>
       <c r="E121" s="2" t="n">
         <f aca="false">(D121-B121)/D121*100</f>
-        <v>0.597206248306137</v>
+        <v>0.597206248306119</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11900,7 +13427,7 @@
       </c>
       <c r="E122" s="2" t="n">
         <f aca="false">(D122-B122)/D122*100</f>
-        <v>0.602209646843841</v>
+        <v>0.602209646843805</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11921,7 +13448,7 @@
       </c>
       <c r="E123" s="2" t="n">
         <f aca="false">(D123-B123)/D123*100</f>
-        <v>0.607212793537528</v>
+        <v>0.607212793537399</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11942,7 +13469,7 @@
       </c>
       <c r="E124" s="2" t="n">
         <f aca="false">(D124-B124)/D124*100</f>
-        <v>0.612215688399914</v>
+        <v>0.612215688399839</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11963,7 +13490,7 @@
       </c>
       <c r="E125" s="2" t="n">
         <f aca="false">(D125-B125)/D125*100</f>
-        <v>0.617218331443651</v>
+        <v>0.6172183314435</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11984,7 +13511,7 @@
       </c>
       <c r="E126" s="2" t="n">
         <f aca="false">(D126-B126)/D126*100</f>
-        <v>0.622220722681401</v>
+        <v>0.622220722681534</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12005,7 +13532,7 @@
       </c>
       <c r="E127" s="2" t="n">
         <f aca="false">(D127-B127)/D127*100</f>
-        <v>0.627222862125874</v>
+        <v>0.627222862125836</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12026,7 +13553,7 @@
       </c>
       <c r="E128" s="2" t="n">
         <f aca="false">(D128-B128)/D128*100</f>
-        <v>0.632224749789731</v>
+        <v>0.632224749789595</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12047,7 +13574,7 @@
       </c>
       <c r="E129" s="2" t="n">
         <f aca="false">(D129-B129)/D129*100</f>
-        <v>0.637226385685628</v>
+        <v>0.637226385685707</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12068,7 +13595,7 @@
       </c>
       <c r="E130" s="2" t="n">
         <f aca="false">(D130-B130)/D130*100</f>
-        <v>0.642227769826241</v>
+        <v>0.642227769826201</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12089,7 +13616,7 @@
       </c>
       <c r="E131" s="2" t="n">
         <f aca="false">(D131-B131)/D131*100</f>
-        <v>0.647228902224249</v>
+        <v>0.647228902224129</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12110,7 +13637,7 @@
       </c>
       <c r="E132" s="2" t="n">
         <f aca="false">(D132-B132)/D132*100</f>
-        <v>0.65222978289233</v>
+        <v>0.652229782892472</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12131,7 +13658,7 @@
       </c>
       <c r="E133" s="2" t="n">
         <f aca="false">(D133-B133)/D133*100</f>
-        <v>0.65723041184315</v>
+        <v>0.657230411843211</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12152,7 +13679,7 @@
       </c>
       <c r="E134" s="2" t="n">
         <f aca="false">(D134-B134)/D134*100</f>
-        <v>0.662230789089389</v>
+        <v>0.662230789089265</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12173,7 +13700,7 @@
       </c>
       <c r="E135" s="2" t="n">
         <f aca="false">(D135-B135)/D135*100</f>
-        <v>0.667230914643714</v>
+        <v>0.667230914643735</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12215,7 +13742,7 @@
       </c>
       <c r="E137" s="2" t="n">
         <f aca="false">(D137-B137)/D137*100</f>
-        <v>0.677230410727242</v>
+        <v>0.677230410727433</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12236,7 +13763,7 @@
       </c>
       <c r="E138" s="2" t="n">
         <f aca="false">(D138-B138)/D138*100</f>
-        <v>0.682229781281789</v>
+        <v>0.682229781281832</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12257,7 +13784,7 @@
       </c>
       <c r="E139" s="2" t="n">
         <f aca="false">(D139-B139)/D139*100</f>
-        <v>0.68722890019508</v>
+        <v>0.687228900194972</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12278,7 +13805,7 @@
       </c>
       <c r="E140" s="2" t="n">
         <f aca="false">(D140-B140)/D140*100</f>
-        <v>0.692227767479792</v>
+        <v>0.692227767479989</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12299,7 +13826,7 @@
       </c>
       <c r="E141" s="2" t="n">
         <f aca="false">(D141-B141)/D141*100</f>
-        <v>0.697226383148609</v>
+        <v>0.697226383148521</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12320,7 +13847,7 @@
       </c>
       <c r="E142" s="2" t="n">
         <f aca="false">(D142-B142)/D142*100</f>
-        <v>0.702224747214155</v>
+        <v>0.702224747214356</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12341,7 +13868,7 @@
       </c>
       <c r="E143" s="2" t="n">
         <f aca="false">(D143-B143)/D143*100</f>
-        <v>0.707222859689122</v>
+        <v>0.707222859689077</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12362,7 +13889,7 @@
       </c>
       <c r="E144" s="2" t="n">
         <f aca="false">(D144-B144)/D144*100</f>
-        <v>0.712220720586143</v>
+        <v>0.71222072058596</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12383,7 +13910,7 @@
       </c>
       <c r="E145" s="2" t="n">
         <f aca="false">(D145-B145)/D145*100</f>
-        <v>0.717218329917916</v>
+        <v>0.7172183299181</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12404,7 +13931,7 @@
       </c>
       <c r="E146" s="2" t="n">
         <f aca="false">(D146-B146)/D146*100</f>
-        <v>0.722215687697082</v>
+        <v>0.722215687697186</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12425,7 +13952,7 @@
       </c>
       <c r="E147" s="2" t="n">
         <f aca="false">(D147-B147)/D147*100</f>
-        <v>0.727212793936317</v>
+        <v>0.727212793936469</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12446,7 +13973,7 @@
       </c>
       <c r="E148" s="2" t="n">
         <f aca="false">(D148-B148)/D148*100</f>
-        <v>0.73220964864828</v>
+        <v>0.732209648648351</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12467,7 +13994,7 @@
       </c>
       <c r="E149" s="2" t="n">
         <f aca="false">(D149-B149)/D149*100</f>
-        <v>0.737206251845613</v>
+        <v>0.737206251845685</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12488,7 +14015,7 @@
       </c>
       <c r="E150" s="2" t="n">
         <f aca="false">(D150-B150)/D150*100</f>
-        <v>0.742202603540999</v>
+        <v>0.74220260354112</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12509,7 +14036,7 @@
       </c>
       <c r="E151" s="2" t="n">
         <f aca="false">(D151-B151)/D151*100</f>
-        <v>0.747198703747078</v>
+        <v>0.7471987037472</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12530,7 +14057,7 @@
       </c>
       <c r="E152" s="2" t="n">
         <f aca="false">(D152-B152)/D152*100</f>
-        <v>0.752194552476521</v>
+        <v>0.752194552476607</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12551,7 +14078,7 @@
       </c>
       <c r="E153" s="2" t="n">
         <f aca="false">(D153-B153)/D153*100</f>
-        <v>0.757190149741988</v>
+        <v>0.757190149741901</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12572,7 +14099,7 @@
       </c>
       <c r="E154" s="2" t="n">
         <f aca="false">(D154-B154)/D154*100</f>
-        <v>0.762185495556127</v>
+        <v>0.76218549555624</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12593,7 +14120,7 @@
       </c>
       <c r="E155" s="2" t="n">
         <f aca="false">(D155-B155)/D155*100</f>
-        <v>0.767180589931612</v>
+        <v>0.767180589931586</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12614,7 +14141,7 @@
       </c>
       <c r="E156" s="2" t="n">
         <f aca="false">(D156-B156)/D156*100</f>
-        <v>0.772175432881063</v>
+        <v>0.772175432881089</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12635,7 +14162,7 @@
       </c>
       <c r="E157" s="2" t="n">
         <f aca="false">(D157-B157)/D157*100</f>
-        <v>0.77717002441717</v>
+        <v>0.777170024417157</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12656,7 +14183,7 @@
       </c>
       <c r="E158" s="2" t="n">
         <f aca="false">(D158-B158)/D158*100</f>
-        <v>0.782164364552584</v>
+        <v>0.782164364552715</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12677,7 +14204,7 @@
       </c>
       <c r="E159" s="2" t="n">
         <f aca="false">(D159-B159)/D159*100</f>
-        <v>0.787158453299948</v>
+        <v>0.787158453299723</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12698,7 +14225,7 @@
       </c>
       <c r="E160" s="2" t="n">
         <f aca="false">(D160-B160)/D160*100</f>
-        <v>0.792152290671909</v>
+        <v>0.792152290671695</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12719,7 +14246,7 @@
       </c>
       <c r="E161" s="2" t="n">
         <f aca="false">(D161-B161)/D161*100</f>
-        <v>0.797145876681141</v>
+        <v>0.797145876680939</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12740,7 +14267,7 @@
       </c>
       <c r="E162" s="2" t="n">
         <f aca="false">(D162-B162)/D162*100</f>
-        <v>0.802139211340276</v>
+        <v>0.802139211340085</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12761,7 +14288,7 @@
       </c>
       <c r="E163" s="2" t="n">
         <f aca="false">(D163-B163)/D163*100</f>
-        <v>0.80713229466199</v>
+        <v>0.807132294662238</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12782,7 +14309,7 @@
       </c>
       <c r="E164" s="2" t="n">
         <f aca="false">(D164-B164)/D164*100</f>
-        <v>0.812125126658904</v>
+        <v>0.812125126659071</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12803,7 +14330,7 @@
       </c>
       <c r="E165" s="2" t="n">
         <f aca="false">(D165-B165)/D165*100</f>
-        <v>0.817117707343695</v>
+        <v>0.817117707343512</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12824,7 +14351,7 @@
       </c>
       <c r="E166" s="2" t="n">
         <f aca="false">(D166-B166)/D166*100</f>
-        <v>0.822110036728992</v>
+        <v>0.822110036729035</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12845,7 +14372,7 @@
       </c>
       <c r="E167" s="2" t="n">
         <f aca="false">(D167-B167)/D167*100</f>
-        <v>0.827102114827456</v>
+        <v>0.827102114827384</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12866,7 +14393,7 @@
       </c>
       <c r="E168" s="2" t="n">
         <f aca="false">(D168-B168)/D168*100</f>
-        <v>0.832093941651742</v>
+        <v>0.832093941651974</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12887,7 +14414,7 @@
       </c>
       <c r="E169" s="2" t="n">
         <f aca="false">(D169-B169)/D169*100</f>
-        <v>0.837085517214484</v>
+        <v>0.837085517214586</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12908,7 +14435,7 @@
       </c>
       <c r="E170" s="2" t="n">
         <f aca="false">(D170-B170)/D170*100</f>
-        <v>0.84207684152831</v>
+        <v>0.842076841528325</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12929,7 +14456,7 @@
       </c>
       <c r="E171" s="2" t="n">
         <f aca="false">(D171-B171)/D171*100</f>
-        <v>0.847067914605897</v>
+        <v>0.847067914605748</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12950,7 +14477,7 @@
       </c>
       <c r="E172" s="2" t="n">
         <f aca="false">(D172-B172)/D172*100</f>
-        <v>0.852058736459898</v>
+        <v>0.852058736460079</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12971,7 +14498,7 @@
       </c>
       <c r="E173" s="2" t="n">
         <f aca="false">(D173-B173)/D173*100</f>
-        <v>0.857049307102942</v>
+        <v>0.857049307102881</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12992,7 +14519,7 @@
       </c>
       <c r="E174" s="2" t="n">
         <f aca="false">(D174-B174)/D174*100</f>
-        <v>0.862039626547661</v>
+        <v>0.862039626547538</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13013,7 +14540,7 @@
       </c>
       <c r="E175" s="2" t="n">
         <f aca="false">(D175-B175)/D175*100</f>
-        <v>0.867029694806736</v>
+        <v>0.867029694806829</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13034,7 +14561,7 @@
       </c>
       <c r="E176" s="2" t="n">
         <f aca="false">(D176-B176)/D176*100</f>
-        <v>0.872019511892771</v>
+        <v>0.872019511892849</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13055,7 +14582,7 @@
       </c>
       <c r="E177" s="2" t="n">
         <f aca="false">(D177-B177)/D177*100</f>
-        <v>0.877009077818446</v>
+        <v>0.877009077818367</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13076,7 +14603,7 @@
       </c>
       <c r="E178" s="2" t="n">
         <f aca="false">(D178-B178)/D178*100</f>
-        <v>0.88199839259636</v>
+        <v>0.881998392596632</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13097,7 +14624,7 @@
       </c>
       <c r="E179" s="2" t="n">
         <f aca="false">(D179-B179)/D179*100</f>
-        <v>0.886987456239172</v>
+        <v>0.88698745623893</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13118,7 +14645,7 @@
       </c>
       <c r="E180" s="2" t="n">
         <f aca="false">(D180-B180)/D180*100</f>
-        <v>0.891976268759542</v>
+        <v>0.891976268759836</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13139,7 +14666,7 @@
       </c>
       <c r="E181" s="2" t="n">
         <f aca="false">(D181-B181)/D181*100</f>
-        <v>0.896964830170102</v>
+        <v>0.896964830170283</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13160,7 +14687,7 @@
       </c>
       <c r="E182" s="2" t="n">
         <f aca="false">(D182-B182)/D182*100</f>
-        <v>0.901953140483488</v>
+        <v>0.901953140483771</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13181,7 +14708,7 @@
       </c>
       <c r="E183" s="2" t="n">
         <f aca="false">(D183-B183)/D183*100</f>
-        <v>0.90694119971232</v>
+        <v>0.906941199712287</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13202,7 +14729,7 @@
       </c>
       <c r="E184" s="2" t="n">
         <f aca="false">(D184-B184)/D184*100</f>
-        <v>0.911929007869261</v>
+        <v>0.911929007869414</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13223,7 +14750,7 @@
       </c>
       <c r="E185" s="2" t="n">
         <f aca="false">(D185-B185)/D185*100</f>
-        <v>0.916916564966928</v>
+        <v>0.916916564967082</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13244,7 +14771,7 @@
       </c>
       <c r="E186" s="2" t="n">
         <f aca="false">(D186-B186)/D186*100</f>
-        <v>0.921903871017988</v>
+        <v>0.921903871018196</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13265,7 +14792,7 @@
       </c>
       <c r="E187" s="2" t="n">
         <f aca="false">(D187-B187)/D187*100</f>
-        <v>0.926890926035049</v>
+        <v>0.926890926035294</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13286,7 +14813,7 @@
       </c>
       <c r="E188" s="2" t="n">
         <f aca="false">(D188-B188)/D188*100</f>
-        <v>0.931877730030754</v>
+        <v>0.931877730030559</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13307,7 +14834,7 @@
       </c>
       <c r="E189" s="2" t="n">
         <f aca="false">(D189-B189)/D189*100</f>
-        <v>0.936864283017734</v>
+        <v>0.936864283017485</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13328,7 +14855,7 @@
       </c>
       <c r="E190" s="2" t="n">
         <f aca="false">(D190-B190)/D190*100</f>
-        <v>0.941850585008656</v>
+        <v>0.941850585008728</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13349,7 +14876,7 @@
       </c>
       <c r="E191" s="2" t="n">
         <f aca="false">(D191-B191)/D191*100</f>
-        <v>0.946836636016108</v>
+        <v>0.946836636016199</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13370,7 +14897,7 @@
       </c>
       <c r="E192" s="2" t="n">
         <f aca="false">(D192-B192)/D192*100</f>
-        <v>0.951822436052737</v>
+        <v>0.951822436052701</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13391,7 +14918,7 @@
       </c>
       <c r="E193" s="2" t="n">
         <f aca="false">(D193-B193)/D193*100</f>
-        <v>0.956807985131198</v>
+        <v>0.956807985130882</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13412,7 +14939,7 @@
       </c>
       <c r="E194" s="2" t="n">
         <f aca="false">(D194-B194)/D194*100</f>
-        <v>0.961793283264099</v>
+        <v>0.961793283263986</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13433,7 +14960,7 @@
       </c>
       <c r="E195" s="2" t="n">
         <f aca="false">(D195-B195)/D195*100</f>
-        <v>0.966778330464073</v>
+        <v>0.966778330464262</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13454,7 +14981,7 @@
       </c>
       <c r="E196" s="2" t="n">
         <f aca="false">(D196-B196)/D196*100</f>
-        <v>0.971763126743773</v>
+        <v>0.97176312674383</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13475,7 +15002,7 @@
       </c>
       <c r="E197" s="2" t="n">
         <f aca="false">(D197-B197)/D197*100</f>
-        <v>0.976747672115819</v>
+        <v>0.976747672116108</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13517,7 +15044,7 @@
       </c>
       <c r="E199" s="2" t="n">
         <f aca="false">(D199-B199)/D199*100</f>
-        <v>0.986716010187409</v>
+        <v>0.986716010187448</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13538,7 +15065,7 @@
       </c>
       <c r="E200" s="2" t="n">
         <f aca="false">(D200-B200)/D200*100</f>
-        <v>0.991699802912245</v>
+        <v>0.991699802912365</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13559,7 +15086,7 @@
       </c>
       <c r="E201" s="2" t="n">
         <f aca="false">(D201-B201)/D201*100</f>
-        <v>0.996683344779919</v>
+        <v>0.99668334478002</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13580,7 +15107,7 @@
       </c>
       <c r="E202" s="2" t="n">
         <f aca="false">(D202-B202)/D202*100</f>
-        <v>1.00166663580309</v>
+        <v>1.00166663580331</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13601,7 +15128,7 @@
       </c>
       <c r="E203" s="2" t="n">
         <f aca="false">(D203-B203)/D203*100</f>
-        <v>1.00664967599434</v>
+        <v>1.00664967599436</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13622,7 +15149,7 @@
       </c>
       <c r="E204" s="2" t="n">
         <f aca="false">(D204-B204)/D204*100</f>
-        <v>1.01163246536634</v>
+        <v>1.01163246536655</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13643,7 +15170,7 @@
       </c>
       <c r="E205" s="2" t="n">
         <f aca="false">(D205-B205)/D205*100</f>
-        <v>1.0166150039317</v>
+        <v>1.01661500393162</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13664,7 +15191,7 @@
       </c>
       <c r="E206" s="2" t="n">
         <f aca="false">(D206-B206)/D206*100</f>
-        <v>1.02159729170302</v>
+        <v>1.02159729170308</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13685,7 +15212,7 @@
       </c>
       <c r="E207" s="2" t="n">
         <f aca="false">(D207-B207)/D207*100</f>
-        <v>1.02657932869295</v>
+        <v>1.02657932869278</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13706,7 +15233,7 @@
       </c>
       <c r="E208" s="2" t="n">
         <f aca="false">(D208-B208)/D208*100</f>
-        <v>1.03156111491412</v>
+        <v>1.03156111491432</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13727,7 +15254,7 @@
       </c>
       <c r="E209" s="2" t="n">
         <f aca="false">(D209-B209)/D209*100</f>
-        <v>1.03654265037913</v>
+        <v>1.03654265037931</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13748,7 +15275,7 @@
       </c>
       <c r="E210" s="2" t="n">
         <f aca="false">(D210-B210)/D210*100</f>
-        <v>1.04152393510061</v>
+        <v>1.04152393510028</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13769,7 +15296,7 @@
       </c>
       <c r="E211" s="2" t="n">
         <f aca="false">(D211-B211)/D211*100</f>
-        <v>1.04650496909118</v>
+        <v>1.04650496909131</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13790,7 +15317,7 @@
       </c>
       <c r="E212" s="2" t="n">
         <f aca="false">(D212-B212)/D212*100</f>
-        <v>1.05148575236348</v>
+        <v>1.05148575236356</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13811,7 +15338,7 @@
       </c>
       <c r="E213" s="2" t="n">
         <f aca="false">(D213-B213)/D213*100</f>
-        <v>1.0564662849301</v>
+        <v>1.05646628493036</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13832,7 +15359,7 @@
       </c>
       <c r="E214" s="2" t="n">
         <f aca="false">(D214-B214)/D214*100</f>
-        <v>1.06144656680368</v>
+        <v>1.0614465668039</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13853,7 +15380,7 @@
       </c>
       <c r="E215" s="2" t="n">
         <f aca="false">(D215-B215)/D215*100</f>
-        <v>1.06642659799681</v>
+        <v>1.0664265979971</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13874,7 +15401,7 @@
       </c>
       <c r="E216" s="2" t="n">
         <f aca="false">(D216-B216)/D216*100</f>
-        <v>1.07140637852215</v>
+        <v>1.071406378522</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13895,7 +15422,7 @@
       </c>
       <c r="E217" s="2" t="n">
         <f aca="false">(D217-B217)/D217*100</f>
-        <v>1.07638590839229</v>
+        <v>1.07638590839231</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13916,7 +15443,7 @@
       </c>
       <c r="E218" s="2" t="n">
         <f aca="false">(D218-B218)/D218*100</f>
-        <v>1.08136518761986</v>
+        <v>1.08136518762028</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13937,7 +15464,7 @@
       </c>
       <c r="E219" s="2" t="n">
         <f aca="false">(D219-B219)/D219*100</f>
-        <v>1.08634421621746</v>
+        <v>1.08634421621789</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13958,7 +15485,7 @@
       </c>
       <c r="E220" s="2" t="n">
         <f aca="false">(D220-B220)/D220*100</f>
-        <v>1.09132299419772</v>
+        <v>1.09132299419785</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13979,7 +15506,7 @@
       </c>
       <c r="E221" s="2" t="n">
         <f aca="false">(D221-B221)/D221*100</f>
-        <v>1.09630152157324</v>
+        <v>1.09630152157335</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14000,7 +15527,7 @@
       </c>
       <c r="E222" s="2" t="n">
         <f aca="false">(D222-B222)/D222*100</f>
-        <v>1.10127979835665</v>
+        <v>1.10127979835676</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14021,7 +15548,7 @@
       </c>
       <c r="E223" s="2" t="n">
         <f aca="false">(D223-B223)/D223*100</f>
-        <v>1.10625782456055</v>
+        <v>1.10625782456019</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14042,7 +15569,7 @@
       </c>
       <c r="E224" s="2" t="n">
         <f aca="false">(D224-B224)/D224*100</f>
-        <v>1.11123560019755</v>
+        <v>1.11123560019759</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14063,7 +15590,7 @@
       </c>
       <c r="E225" s="2" t="n">
         <f aca="false">(D225-B225)/D225*100</f>
-        <v>1.11621312528027</v>
+        <v>1.11621312528031</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14084,7 +15611,7 @@
       </c>
       <c r="E226" s="2" t="n">
         <f aca="false">(D226-B226)/D226*100</f>
-        <v>1.12119039982134</v>
+        <v>1.12119039982152</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14105,7 +15632,7 @@
       </c>
       <c r="E227" s="2" t="n">
         <f aca="false">(D227-B227)/D227*100</f>
-        <v>1.12616742383333</v>
+        <v>1.12616742383302</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14126,7 +15653,7 @@
       </c>
       <c r="E228" s="2" t="n">
         <f aca="false">(D228-B228)/D228*100</f>
-        <v>1.13114419732889</v>
+        <v>1.13114419732885</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14147,7 +15674,7 @@
       </c>
       <c r="E229" s="2" t="n">
         <f aca="false">(D229-B229)/D229*100</f>
-        <v>1.13612072032061</v>
+        <v>1.13612072032042</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14168,7 +15695,7 @@
       </c>
       <c r="E230" s="2" t="n">
         <f aca="false">(D230-B230)/D230*100</f>
-        <v>1.1410969928211</v>
+        <v>1.14109699282063</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14189,7 +15716,7 @@
       </c>
       <c r="E231" s="2" t="n">
         <f aca="false">(D231-B231)/D231*100</f>
-        <v>1.14607301484297</v>
+        <v>1.14607301484258</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14210,7 +15737,7 @@
       </c>
       <c r="E232" s="2" t="n">
         <f aca="false">(D232-B232)/D232*100</f>
-        <v>1.15104878639883</v>
+        <v>1.15104878639908</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14231,7 +15758,7 @@
       </c>
       <c r="E233" s="2" t="n">
         <f aca="false">(D233-B233)/D233*100</f>
-        <v>1.1560243075013</v>
+        <v>1.15602430750134</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14252,7 +15779,7 @@
       </c>
       <c r="E234" s="2" t="n">
         <f aca="false">(D234-B234)/D234*100</f>
-        <v>1.16099957816294</v>
+        <v>1.1609995781629</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14273,7 +15800,7 @@
       </c>
       <c r="E235" s="2" t="n">
         <f aca="false">(D235-B235)/D235*100</f>
-        <v>1.16597459839641</v>
+        <v>1.16597459839645</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14294,7 +15821,7 @@
       </c>
       <c r="E236" s="2" t="n">
         <f aca="false">(D236-B236)/D236*100</f>
-        <v>1.17094936821429</v>
+        <v>1.17094936821427</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14315,7 +15842,7 @@
       </c>
       <c r="E237" s="2" t="n">
         <f aca="false">(D237-B237)/D237*100</f>
-        <v>1.1759238876292</v>
+        <v>1.17592388762918</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14336,7 +15863,7 @@
       </c>
       <c r="E238" s="2" t="n">
         <f aca="false">(D238-B238)/D238*100</f>
-        <v>1.18089815665371</v>
+        <v>1.18089815665377</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14357,7 +15884,7 @@
       </c>
       <c r="E239" s="2" t="n">
         <f aca="false">(D239-B239)/D239*100</f>
-        <v>1.18587217530046</v>
+        <v>1.18587217530051</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14378,7 +15905,7 @@
       </c>
       <c r="E240" s="2" t="n">
         <f aca="false">(D240-B240)/D240*100</f>
-        <v>1.19084594358203</v>
+        <v>1.19084594358204</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14399,7 +15926,7 @@
       </c>
       <c r="E241" s="2" t="n">
         <f aca="false">(D241-B241)/D241*100</f>
-        <v>1.19581946151101</v>
+        <v>1.19581946151097</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14420,7 +15947,7 @@
       </c>
       <c r="E242" s="2" t="n">
         <f aca="false">(D242-B242)/D242*100</f>
-        <v>1.20079272910004</v>
+        <v>1.20079272910003</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14441,7 +15968,7 @@
       </c>
       <c r="E243" s="2" t="n">
         <f aca="false">(D243-B243)/D243*100</f>
-        <v>1.2057657463617</v>
+        <v>1.20576574636167</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14462,7 +15989,7 @@
       </c>
       <c r="E244" s="2" t="n">
         <f aca="false">(D244-B244)/D244*100</f>
-        <v>1.2107385133086</v>
+        <v>1.21073851330856</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14483,7 +16010,7 @@
       </c>
       <c r="E245" s="2" t="n">
         <f aca="false">(D245-B245)/D245*100</f>
-        <v>1.21571102995332</v>
+        <v>1.21571102995339</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/develop/day22-excel-file.xlsx
+++ b/develop/day22-excel-file.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,24 +22,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="5">
+  <si>
+    <t xml:space="preserve">t</t>
+  </si>
   <si>
     <t xml:space="preserve">x</t>
   </si>
   <si>
-    <t xml:space="preserve">y</t>
+    <t xml:space="preserve">dxdt</t>
   </si>
   <si>
-    <t xml:space="preserve">dy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f(X)</t>
+    <t xml:space="preserve">f(t)</t>
   </si>
   <si>
     <t xml:space="preserve">error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f(x)</t>
   </si>
 </sst>
 </file>
@@ -49,7 +46,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,11 +85,6 @@
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -242,7 +234,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>y</c:v>
+                  <c:v>x</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1072,7 +1064,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>f(X)</c:v>
+                  <c:v>f(t)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1893,11 +1885,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="17228425"/>
-        <c:axId val="29927723"/>
+        <c:axId val="46810543"/>
+        <c:axId val="93170277"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="17228425"/>
+        <c:axId val="46810543"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1928,12 +1920,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29927723"/>
+        <c:crossAx val="93170277"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="29927723"/>
+        <c:axId val="93170277"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1973,7 +1965,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17228425"/>
+        <c:crossAx val="46810543"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2077,7 +2069,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>y</c:v>
+                  <c:v>x</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2898,11 +2890,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="91438552"/>
-        <c:axId val="40506022"/>
+        <c:axId val="36052914"/>
+        <c:axId val="86608577"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="91438552"/>
+        <c:axId val="36052914"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2944,12 +2936,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40506022"/>
+        <c:crossAx val="86608577"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="40506022"/>
+        <c:axId val="86608577"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2991,7 +2983,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91438552"/>
+        <c:crossAx val="36052914"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3062,7 +3054,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>y</c:v>
+                  <c:v>x</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3091,11 +3083,15 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -4608,7 +4604,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>f(x)</c:v>
+                  <c:v>f(t)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4637,11 +4633,15 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -6145,17 +6145,17 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="61199096"/>
-        <c:axId val="22753671"/>
+        <c:axId val="80508457"/>
+        <c:axId val="50246474"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="61199096"/>
+        <c:axId val="80508457"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -6172,17 +6172,20 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22753671"/>
+        <c:crossAx val="50246474"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="22753671"/>
+        <c:axId val="50246474"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6197,7 +6200,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -6214,14 +6217,17 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61199096"/>
+        <c:crossAx val="80508457"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -6247,6 +6253,9 @@
         <a:p>
           <a:pPr>
             <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
               <a:latin typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -6278,9 +6287,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>335160</xdr:colOff>
+      <xdr:colOff>334800</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>255600</xdr:rowOff>
+      <xdr:rowOff>255240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6289,7 +6298,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7908480" y="703440"/>
-        <a:ext cx="5764680" cy="3241440"/>
+        <a:ext cx="5764320" cy="3241080"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6313,9 +6322,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>543600</xdr:colOff>
+      <xdr:colOff>543240</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>92520</xdr:rowOff>
+      <xdr:rowOff>92160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6324,7 +6333,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="2912760" y="398520"/>
-        <a:ext cx="5195520" cy="2742120"/>
+        <a:ext cx="5195160" cy="2741760"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6348,9 +6357,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>634680</xdr:colOff>
+      <xdr:colOff>634320</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>183240</xdr:rowOff>
+      <xdr:rowOff>182880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6359,7 +6368,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="3816360" y="564120"/>
-        <a:ext cx="5758560" cy="3238560"/>
+        <a:ext cx="5758200" cy="3238200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -10884,7 +10893,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
